--- a/MinMax/scripts/comparison/time_totals_118.xlsx
+++ b/MinMax/scripts/comparison/time_totals_118.xlsx
@@ -46,25 +46,25 @@
     <t>Vr Vi Warm Start True</t>
   </si>
   <si>
-    <t>[3.4737861156463623, 2.6687960624694824]</t>
-  </si>
-  <si>
-    <t>[5.561622142791748, 5.248106956481934]</t>
-  </si>
-  <si>
-    <t>[1.226243019104004, 1.9601049423217773]</t>
-  </si>
-  <si>
-    <t>[2.196418046951294, 2.3951590061187744]</t>
-  </si>
-  <si>
-    <t>[5.426153898239136, 9.123433828353882]</t>
-  </si>
-  <si>
-    <t>[1.1923720836639404, 0.9612998962402344]</t>
-  </si>
-  <si>
-    <t>[6.921187877655029, 5.979217052459717]</t>
+    <t>[0.244520902633667, 0.24456501007080078, 0.2445690631866455, 0.24462103843688965, 0.2446269989013672, 0.24467206001281738, 0.2446901798248291, 0.2447049617767334, 0.24475502967834473, 0.24479103088378906, 0.24479198455810547, 0.24485087394714355, 0.24490594863891602, 0.24491405487060547, 0.2449648380279541, 0.24510598182678223, 0.24512290954589844, 0.24514102935791016, 0.24521589279174805, 0.24521684646606445, 0.24524497985839844, 0.24535298347473145, 0.24538898468017578, 0.2454080581665039, 0.2454240322113037, 0.24542593955993652, 0.2454378604888916, 0.2455439567565918, 0.24555087089538574, 0.24562788009643555, 0.2456350326538086, 0.24567699432373047, 0.24571800231933594, 0.24573206901550293, 0.24573588371276855, 0.24573898315429688, 0.24575400352478027, 0.24575591087341309, 0.24587082862854004, 0.245880126953125, 0.24589204788208008, 0.2458961009979248, 0.2459118366241455, 0.24592304229736328, 0.2459239959716797, 0.2459239959716797, 0.24596786499023438, 0.24599909782409668, 0.246107816696167, 0.24615907669067383, 0.24622511863708496, 0.24622893333435059, 0.24624300003051758, 0.24628877639770508, 0.24632787704467773, 0.24634480476379395, 0.24645709991455078, 0.24652504920959473, 0.2466139793395996, 0.24665617942810059, 0.2466728687286377, 0.2466881275177002, 0.2467029094696045, 0.2467508316040039, 0.24678611755371094, 0.24678993225097656, 0.2469329833984375, 0.24694108963012695, 0.24696898460388184, 0.246992826461792, 0.2470560073852539, 0.2471790313720703, 0.2472231388092041, 0.24736499786376953, 0.24738097190856934, 0.24739885330200195, 0.2474050521850586, 0.24750995635986328, 0.24758601188659668, 0.24760699272155762, 0.2478618621826172, 0.24793004989624023, 0.24808597564697266, 0.24812984466552734, 0.24845504760742188, 0.2487790584564209, 0.25066709518432617, 0.2514798641204834, 0.2543659210205078, 0.2546219825744629, 0.2546350955963135, 0.2547459602355957, 0.25477099418640137, 0.25478100776672363, 0.25479602813720703, 0.2548239231109619, 0.25487208366394043, 0.2548799514770508, 0.2549309730529785, 0.25496912002563477, 0.25497007369995117, 0.2550809383392334, 0.2551078796386719, 0.2551238536834717, 0.25513386726379395, 0.25513505935668945, 0.25513601303100586, 0.2551870346069336, 0.2551920413970947, 0.255216121673584, 0.2552769184112549, 0.2552788257598877, 0.2553110122680664, 0.2553138732910156, 0.25531888008117676, 0.25531983375549316, 0.25536203384399414, 0.2553880214691162, 0.25540590286254883, 0.25540804862976074, 0.25543999671936035, 0.25544309616088867, 0.2554609775543213, 0.25547099113464355, 0.25551390647888184, 0.2555389404296875, 0.25557804107666016, 0.2556030750274658, 0.25560498237609863, 0.25560998916625977, 0.2556300163269043, 0.25564002990722656, 0.25565218925476074, 0.25565290451049805, 0.2556571960449219, 0.2556588649749756, 0.2556650638580322, 0.25566887855529785, 0.25567007064819336, 0.2556748390197754, 0.25568509101867676, 0.2556891441345215, 0.2556920051574707, 0.25569701194763184, 0.25569987297058105, 0.25570201873779297, 0.2557048797607422, 0.2557108402252197, 0.25571179389953613, 0.2557408809661865, 0.2557528018951416, 0.25576090812683105, 0.2557661533355713, 0.25580286979675293, 0.2558128833770752, 0.25585293769836426, 0.25585484504699707, 0.2558591365814209, 0.2558598518371582, 0.25587987899780273, 0.2558860778808594, 0.2558910846710205, 0.25591087341308594, 0.2559220790863037, 0.25592589378356934, 0.2559349536895752, 0.2559380531311035, 0.2559478282928467, 0.2559521198272705, 0.25595903396606445, 0.2559659481048584, 0.2559671401977539, 0.2559831142425537, 0.2559850215911865, 0.2559969425201416, 0.25600481033325195, 0.2560129165649414, 0.2560150623321533, 0.2560231685638428, 0.2560279369354248, 0.25603413581848145, 0.25604915618896484, 0.25605297088623047, 0.25606703758239746, 0.25609493255615234, 0.2561018466949463, 0.256105899810791, 0.25614380836486816, 0.2561640739440918, 0.2561650276184082, 0.256166934967041, 0.2561819553375244, 0.2561838626861572, 0.25620198249816895, 0.25624680519104004, 0.25624799728393555, 0.2562520503997803, 0.2562580108642578, 0.2562699317932129, 0.2562708854675293, 0.25627613067626953, 0.2562830448150635, 0.2562870979309082, 0.2563049793243408, 0.2563209533691406, 0.25632786750793457, 0.25634098052978516, 0.2563490867614746, 0.2563750743865967, 0.25638508796691895, 0.256389856338501, 0.2563900947570801, 0.2563908100128174, 0.2563951015472412, 0.25639915466308594, 0.25640320777893066, 0.2564358711242676, 0.2564389705657959, 0.2564389705657959, 0.2564511299133301, 0.2564520835876465, 0.25645899772644043, 0.25646495819091797, 0.2564709186553955, 0.25647807121276855, 0.2564990520477295, 0.2565019130706787, 0.2565031051635742, 0.2565150260925293, 0.2565300464630127, 0.25653886795043945, 0.25656890869140625, 0.2565732002258301, 0.25661182403564453, 0.2566211223602295, 0.25662803649902344, 0.2566359043121338, 0.2566409111022949, 0.2566540241241455, 0.2566559314727783, 0.25666379928588867, 0.2566690444946289, 0.25667881965637207, 0.2566800117492676, 0.25669217109680176, 0.25672197341918945, 0.25674009323120117, 0.25675296783447266, 0.2567570209503174, 0.2567710876464844, 0.2567870616912842, 0.2567899227142334, 0.256821870803833, 0.25683093070983887, 0.2568340301513672, 0.2568349838256836, 0.2568359375, 0.2568819522857666, 0.2568838596343994, 0.25689196586608887, 0.2568931579589844, 0.2568948268890381, 0.256925106048584, 0.25693416595458984, 0.25693511962890625, 0.2569389343261719, 0.25695300102233887, 0.2569549083709717, 0.2569570541381836, 0.25696420669555664, 0.2569718360900879, 0.2569730281829834, 0.25697803497314453, 0.25698208808898926, 0.2569880485534668, 0.2569890022277832, 0.25699782371520996, 0.2570009231567383, 0.257004976272583, 0.2570178508758545, 0.25702786445617676, 0.257037878036499, 0.2570509910583496, 0.25705599784851074, 0.257066011428833, 0.2570669651031494, 0.2570769786834717, 0.2570829391479492, 0.25711989402770996, 0.2571380138397217, 0.25714111328125, 0.2571530342102051, 0.2571578025817871, 0.25716590881347656, 0.2571849822998047, 0.2572000026702881, 0.25722599029541016, 0.25724291801452637, 0.2572469711303711, 0.2572751045227051, 0.25728607177734375, 0.25729799270629883, 0.25730204582214355, 0.2573070526123047, 0.25731515884399414, 0.2573280334472656, 0.25733399391174316, 0.25734710693359375, 0.25735998153686523, 0.2573699951171875, 0.25737500190734863, 0.2574038505554199, 0.25742411613464355, 0.257457971572876, 0.2574801445007324, 0.25749993324279785, 0.25749993324279785, 0.25750088691711426, 0.25750207901000977, 0.25751614570617676, 0.2575409412384033, 0.2575521469116211, 0.2575819492340088, 0.25758910179138184, 0.25759291648864746, 0.25760602951049805, 0.25760698318481445, 0.25760793685913086, 0.25764012336730957, 0.257659912109375, 0.2576889991760254, 0.2577049732208252, 0.2577240467071533, 0.25772714614868164, 0.2577359676361084, 0.2577519416809082, 0.2577650547027588, 0.2577669620513916, 0.2577698230743408, 0.2577829360961914, 0.25781917572021484, 0.25783491134643555, 0.25783681869506836, 0.25783801078796387, 0.2578411102294922, 0.25784993171691895, 0.25785398483276367, 0.2578749656677246, 0.257918119430542, 0.2579329013824463, 0.2579379081726074, 0.2579619884490967, 0.25798988342285156, 0.25799012184143066, 0.2579948902130127, 0.25799989700317383, 0.2580142021179199, 0.2580239772796631, 0.2580249309539795, 0.2580599784851074, 0.25806117057800293, 0.25806188583374023, 0.25806593894958496, 0.25809407234191895, 0.25809597969055176, 0.2581040859222412, 0.2581179141998291, 0.2581210136413574, 0.25812506675720215, 0.2581307888031006, 0.25815391540527344, 0.25817203521728516, 0.25817394256591797, 0.2581820487976074, 0.25820398330688477, 0.25820493698120117, 0.2582099437713623, 0.2582130432128906, 0.25824594497680664, 0.2582979202270508, 0.25832200050354004, 0.2584052085876465, 0.25841712951660156, 0.25842809677124023, 0.25843214988708496, 0.2584390640258789, 0.25845789909362793, 0.25846409797668457, 0.2584860324859619, 0.2584969997406006, 0.2585029602050781, 0.25852298736572266, 0.25855112075805664, 0.2586030960083008, 0.25861215591430664, 0.2587161064147949, 0.2588460445404053, 0.2588980197906494, 0.25892114639282227, 0.2589559555053711, 0.2589890956878662, 0.25899505615234375, 0.2590458393096924, 0.25908613204956055, 0.25914597511291504, 0.2591850757598877, 0.25955820083618164, 0.2598710060119629, 0.2599070072174072, 0.2600541114807129, 0.2601308822631836, 0.2610490322113037, 0.26111507415771484, 0.2612159252166748, 0.2628469467163086, 0.26329612731933594, 0.2652161121368408, 0.2654440402984619, 0.2654581069946289, 0.2654879093170166, 0.26555299758911133, 0.26555800437927246, 0.26561689376831055, 0.26568078994750977, 0.26570796966552734, 0.2657592296600342, 0.2657771110534668, 0.26581382751464844, 0.2658569812774658, 0.26587581634521484, 0.2658979892730713, 0.2659311294555664, 0.26596593856811523, 0.2659878730773926, 0.26602816581726074, 0.26603198051452637, 0.2660350799560547, 0.2660391330718994, 0.2660510540008545, 0.26607608795166016, 0.2661001682281494, 0.266124963760376, 0.2661430835723877, 0.2661750316619873, 0.26620006561279297, 0.26622700691223145, 0.26622700691223145, 0.266232967376709, 0.2662358283996582, 0.2662389278411865, 0.26625800132751465, 0.26627302169799805, 0.2662811279296875, 0.2662980556488037, 0.2663002014160156, 0.26632189750671387, 0.26635098457336426, 0.26637911796569824, 0.26641416549682617, 0.26642894744873047, 0.2664339542388916, 0.2664508819580078, 0.2664811611175537, 0.26653099060058594, 0.2665550708770752, 0.26656413078308105, 0.26656484603881836, 0.26659703254699707, 0.2666289806365967, 0.2666339874267578, 0.26664090156555176, 0.26664280891418457, 0.26665401458740234, 0.26665616035461426, 0.26666688919067383, 0.2666740417480469, 0.26668596267700195, 0.2666900157928467, 0.26670384407043457, 0.26673007011413574, 0.26674389839172363, 0.26674604415893555, 0.2667510509490967, 0.26676082611083984, 0.26677393913269043, 0.2667808532714844, 0.2667958736419678, 0.2668190002441406, 0.26683807373046875, 0.2668778896331787, 0.26689791679382324, 0.266909122467041, 0.26691293716430664, 0.2669188976287842, 0.2669229507446289, 0.26692795753479004, 0.26699399948120117, 0.26701903343200684, 0.2670309543609619, 0.26705312728881836, 0.26706910133361816, 0.2670760154724121, 0.26708197593688965, 0.2671089172363281, 0.26711201667785645, 0.26718688011169434, 0.26718783378601074, 0.26720094680786133, 0.2672088146209717, 0.2672131061553955, 0.2672309875488281, 0.2672410011291504, 0.2672579288482666, 0.26726698875427246, 0.26727795600891113, 0.26729393005371094, 0.26732611656188965, 0.26732802391052246, 0.26733994483947754, 0.2673461437225342, 0.2673640251159668, 0.2673909664154053, 0.26740407943725586, 0.267409086227417, 0.26743507385253906, 0.2674441337585449, 0.26746201515197754, 0.267488956451416, 0.2675178050994873, 0.26752400398254395, 0.2675471305847168, 0.2675650119781494, 0.2675800323486328, 0.26758813858032227, 0.2676219940185547, 0.26762986183166504, 0.2676370143890381, 0.26764607429504395, 0.26764607429504395, 0.26764798164367676, 0.2676680088043213, 0.2676689624786377, 0.26767587661743164, 0.2676870822906494, 0.26771092414855957, 0.267758846282959, 0.26777195930480957, 0.26778388023376465, 0.26779794692993164, 0.2678039073944092, 0.2678079605102539, 0.26781296730041504, 0.2678380012512207, 0.26785802841186523, 0.26785898208618164, 0.26786088943481445, 0.26788997650146484, 0.26789188385009766, 0.2679109573364258, 0.2679319381713867, 0.26795005798339844, 0.2679629325866699, 0.26796984672546387, 0.2679929733276367, 0.26802992820739746, 0.26804685592651367, 0.2680690288543701, 0.2680790424346924, 0.2680940628051758, 0.2680950164794922, 0.26810717582702637, 0.26810789108276367, 0.2681150436401367, 0.2681310176849365, 0.2681398391723633, 0.26816511154174805, 0.2681729793548584, 0.2681729793548584, 0.2681889533996582, 0.2682058811187744, 0.2682158946990967, 0.2682220935821533, 0.2682511806488037, 0.26825499534606934, 0.26825809478759766, 0.2682669162750244, 0.2683079242706299, 0.26833009719848633, 0.2683570384979248, 0.2683589458465576, 0.26836109161376953, 0.2683689594268799, 0.2683858871459961, 0.26839399337768555, 0.26839780807495117, 0.2684049606323242, 0.26842403411865234, 0.26847410202026367, 0.2684919834136963, 0.2685260772705078, 0.2685511112213135, 0.268557071685791, 0.26856088638305664, 0.2685861587524414, 0.26859498023986816, 0.268604040145874, 0.2686188220977783, 0.2686500549316406, 0.2686800956726074, 0.2686882019042969, 0.2686929702758789, 0.26869797706604004, 0.268726110458374, 0.26879215240478516, 0.26883983612060547, 0.268841028213501, 0.2688589096069336, 0.26886582374572754, 0.26886916160583496, 0.26891207695007324, 0.26891398429870605, 0.26892781257629395, 0.268934965133667, 0.26899099349975586, 0.26899290084838867, 0.2689969539642334, 0.26900720596313477, 0.2690598964691162, 0.26907896995544434, 0.26909494400024414, 0.26911497116088867, 0.2691209316253662, 0.2691481113433838, 0.269150972366333, 0.2691538333892822, 0.269179105758667, 0.26920390129089355, 0.26921701431274414, 0.26927709579467773, 0.2692909240722656, 0.269366979598999, 0.26940011978149414, 0.269428014755249, 0.2694969177246094, 0.2695159912109375, 0.2695441246032715, 0.2696390151977539, 0.26979613304138184, 0.2699160575866699, 0.26992297172546387, 0.2701568603515625, 0.27021002769470215, 0.2702310085296631, 0.2702491283416748, 0.27041077613830566, 0.270460844039917, 0.2705080509185791, 0.27054810523986816, 0.2706170082092285, 0.27135181427001953, 0.27140307426452637, 0.27163219451904297, 0.2719390392303467, 0.2722899913787842, 0.2723088264465332, 0.27345800399780273, 0.2735729217529297, 0.27585792541503906, 0.2761659622192383, 0.276202917098999, 0.27626490592956543, 0.27657604217529297, 0.2766580581665039, 0.27672886848449707, 0.2767369747161865, 0.27681589126586914, 0.27685093879699707, 0.276885986328125, 0.27689695358276367, 0.2769050598144531, 0.27697181701660156, 0.27704906463623047, 0.2770500183105469, 0.27707409858703613, 0.27707409858703613, 0.27724194526672363, 0.2772789001464844, 0.27728891372680664, 0.2773771286010742, 0.2773909568786621, 0.27741098403930664, 0.27744579315185547, 0.27745985984802246, 0.2774779796600342, 0.2774820327758789, 0.2775399684906006, 0.2776200771331787, 0.27764391899108887, 0.27766895294189453, 0.27770304679870605, 0.27773499488830566, 0.2778458595275879, 0.2778480052947998, 0.2778589725494385, 0.2778921127319336, 0.27789998054504395, 0.27793192863464355, 0.27796196937561035, 0.2780039310455322, 0.2780148983001709, 0.27813005447387695, 0.2782158851623535, 0.2782161235809326, 0.2782299518585205, 0.2783010005950928, 0.27832984924316406, 0.2783670425415039, 0.2783818244934082, 0.2783851623535156, 0.27838706970214844, 0.278393030166626, 0.2784249782562256, 0.27845311164855957, 0.27846503257751465, 0.2784698009490967, 0.27852416038513184, 0.2785329818725586, 0.2785520553588867, 0.278562068939209, 0.27858591079711914, 0.27858781814575195, 0.278594970703125, 0.27860093116760254, 0.2786109447479248, 0.27870702743530273, 0.27871203422546387, 0.2787189483642578, 0.27878808975219727, 0.2787959575653076, 0.27881598472595215, 0.2788219451904297, 0.27884602546691895, 0.27885985374450684, 0.2788839340209961, 0.27889084815979004, 0.27889108657836914, 0.27892494201660156, 0.2789289951324463, 0.27899622917175293, 0.2790191173553467, 0.27902913093566895, 0.27903294563293457, 0.27907681465148926, 0.2790980339050293, 0.2791900634765625, 0.2792069911956787, 0.27927112579345703, 0.2793560028076172, 0.2793769836425781, 0.27942395210266113, 0.27943992614746094, 0.27951788902282715, 0.27952098846435547, 0.2795231342315674, 0.27954888343811035, 0.27956104278564453, 0.27958202362060547, 0.279616117477417, 0.2796518802642822, 0.2796788215637207, 0.2796812057495117, 0.27973198890686035, 0.2797579765319824, 0.27976202964782715, 0.2799220085144043, 0.27994418144226074, 0.28000497817993164, 0.2801210880279541, 0.2801370620727539, 0.28018808364868164, 0.28020215034484863, 0.2802150249481201, 0.2802588939666748, 0.2802879810333252, 0.2803189754486084, 0.28041791915893555, 0.2806849479675293, 0.28095197677612305, 0.2810819149017334, 0.2811582088470459, 0.2812771797180176, 0.2812840938568115, 0.281735897064209, 0.2819030284881592, 0.28205418586730957, 0.28229808807373047, 0.28231287002563477, 0.2835850715637207, 0.2836880683898926, 0.2855241298675537, 0.28783607482910156, 0.28833818435668945, 0.28892087936401367, 0.28922200202941895, 0.2892310619354248, 0.2894630432128906, 0.2895681858062744, 0.28972315788269043, 0.28989386558532715, 0.2899491786956787, 0.2899589538574219, 0.29002904891967773, 0.29003190994262695, 0.29016685485839844, 0.2903580665588379, 0.29039907455444336, 0.2905399799346924, 0.29066896438598633, 0.2907841205596924, 0.2908649444580078, 0.2911529541015625, 0.2912600040435791, 0.2912778854370117, 0.291363000869751, 0.2914109230041504, 0.2914881706237793, 0.29170894622802734, 0.29175305366516113, 0.29193615913391113, 0.29208898544311523, 0.2921559810638428, 0.2922170162200928, 0.29229307174682617, 0.2926630973815918, 0.29283809661865234, 0.2928628921508789, 0.29328298568725586, 0.29334092140197754, 0.29337191581726074, 0.2934250831604004, 0.29450201988220215, 0.29456520080566406, 0.29510498046875, 0.29538607597351074, 0.2963521480560303, 0.2964189052581787, 0.29651594161987305, 0.29691386222839355, 0.29730701446533203, 0.2991950511932373, 0.3002328872680664, 0.3002431392669678, 0.30030012130737305, 0.30034685134887695, 0.3004119396209717, 0.30042195320129395, 0.3004920482635498, 0.3006560802459717, 0.3007340431213379, 0.3007819652557373, 0.30081892013549805, 0.30086493492126465, 0.30095601081848145, 0.30104517936706543, 0.3010580539703369, 0.30107903480529785, 0.3010900020599365, 0.3011190891265869, 0.3011741638183594, 0.3011770248413086, 0.30118608474731445, 0.3013458251953125, 0.30138301849365234, 0.3014678955078125, 0.30147409439086914, 0.3014841079711914, 0.30153608322143555, 0.3016939163208008, 0.30172204971313477, 0.30174708366394043, 0.3017919063568115, 0.301893949508667, 0.301969051361084, 0.3020508289337158, 0.30220794677734375, 0.3022181987762451, 0.3022439479827881, 0.3023090362548828, 0.3025038242340088, 0.3025228977203369, 0.302839994430542, 0.3028590679168701, 0.3028988838195801, 0.3030660152435303, 0.3030691146850586, 0.3031129837036133, 0.30332398414611816, 0.30333614349365234, 0.3033440113067627, 0.30344390869140625, 0.30364108085632324, 0.30369997024536133, 0.3038291931152344, 0.30386900901794434, 0.3039119243621826, 0.303926944732666, 0.30396080017089844, 0.3041079044342041, 0.3041388988494873, 0.30429911613464355, 0.3050038814544678, 0.30518198013305664, 0.30531907081604004, 0.305401086807251, 0.30542492866516113, 0.3055441379547119, 0.30624914169311523, 0.30632781982421875, 0.3065028190612793, 0.3068208694458008, 0.30713987350463867, 0.30724620819091797, 0.30798888206481934, 0.3088340759277344, 0.31093382835388184, 0.3109409809112549, 0.3114800453186035, 0.31148195266723633, 0.31187891960144043, 0.3119051456451416, 0.3119800090789795, 0.31209301948547363, 0.3121159076690674, 0.3123769760131836, 0.31285715103149414, 0.31292080879211426, 0.31296205520629883, 0.31296610832214355, 0.31311798095703125, 0.3131251335144043, 0.3133389949798584, 0.3133809566497803, 0.31359314918518066, 0.31363391876220703, 0.3140430450439453, 0.3141341209411621, 0.31418585777282715, 0.3142528533935547, 0.31441402435302734, 0.3144669532775879, 0.3150501251220703, 0.31505489349365234, 0.31528592109680176, 0.3153219223022461, 0.31534409523010254, 0.3154120445251465, 0.31610989570617676, 0.31636810302734375, 0.3164341449737549, 0.3164520263671875, 0.3165609836578369, 0.31688690185546875, 0.31697797775268555, 0.31719303131103516, 0.317551851272583, 0.317730188369751, 0.3179938793182373, 0.3192150592803955, 0.3194890022277832, 0.3227579593658447, 0.3230628967285156, 0.32472991943359375, 0.3274540901184082, 0.32750821113586426, 0.3276050090789795, 0.3281819820404053, 0.3285031318664551, 0.3289010524749756, 0.33029603958129883, 0.3332369327545166]</t>
+  </si>
+  <si>
+    <t>[0.29192113876342773, 0.2919628620147705, 0.2919919490814209, 0.29213690757751465, 0.2922048568725586, 0.29224205017089844, 0.29224300384521484, 0.2922549247741699, 0.2926819324493408, 0.29314112663269043, 0.29407501220703125, 0.29441404342651367, 0.2946431636810303, 0.29465484619140625, 0.2967250347137451, 0.2992420196533203, 0.30148911476135254, 0.30159711837768555, 0.3016209602355957, 0.3019840717315674, 0.3020482063293457, 0.3021090030670166, 0.3022150993347168, 0.3022499084472656, 0.30234313011169434, 0.3023688793182373, 0.30239200592041016, 0.30249500274658203, 0.30254101753234863, 0.3027150630950928, 0.3027229309082031, 0.3027689456939697, 0.30280590057373047, 0.30284810066223145, 0.30287790298461914, 0.30290794372558594, 0.302929162979126, 0.30304813385009766, 0.3032500743865967, 0.3033108711242676, 0.3033130168914795, 0.3033270835876465, 0.3034050464630127, 0.30342888832092285, 0.303455114364624, 0.3034989833831787, 0.30352187156677246, 0.30353283882141113, 0.3035728931427002, 0.30361318588256836, 0.3036370277404785, 0.3037071228027344, 0.3037090301513672, 0.30373311042785645, 0.30381202697753906, 0.30399513244628906, 0.3040010929107666, 0.30400800704956055, 0.30403685569763184, 0.30405712127685547, 0.30407190322875977, 0.3042268753051758, 0.3042471408843994, 0.3043029308319092, 0.30443882942199707, 0.3044431209564209, 0.3044569492340088, 0.3044710159301758, 0.3045990467071533, 0.304624080657959, 0.3048579692840576, 0.30500197410583496, 0.30536413192749023, 0.3054358959197998, 0.3054370880126953, 0.30556201934814453, 0.305678129196167, 0.30584096908569336, 0.30584287643432617, 0.30596399307250977, 0.3059840202331543, 0.30616092681884766, 0.30634593963623047, 0.30657196044921875, 0.3066229820251465, 0.3067159652709961, 0.30673694610595703, 0.306790828704834, 0.3073580265045166, 0.3111128807067871, 0.3117711544036865, 0.31224608421325684, 0.3125569820404053, 0.3128221035003662, 0.31282591819763184, 0.31284403800964355, 0.3128499984741211, 0.3128631114959717, 0.31298398971557617, 0.3130660057067871, 0.313068151473999, 0.3130788803100586, 0.3130910396575928, 0.3130989074707031, 0.3131070137023926, 0.3131990432739258, 0.31320619583129883, 0.31322193145751953, 0.31331896781921387, 0.31334805488586426, 0.313352108001709, 0.31336402893066406, 0.31339502334594727, 0.3133981227874756, 0.31342315673828125, 0.3134338855743408, 0.3134448528289795, 0.3134880065917969, 0.3135521411895752, 0.3135550022125244, 0.31355786323547363, 0.3135690689086914, 0.3136310577392578, 0.31363892555236816, 0.3136591911315918, 0.3136599063873291, 0.31367993354797363, 0.3137049674987793, 0.3137080669403076, 0.313709020614624, 0.3137211799621582, 0.3137221336364746, 0.31374692916870117, 0.3137650489807129, 0.31377100944519043, 0.3137810230255127, 0.3137969970703125, 0.3138389587402344, 0.3138618469238281, 0.31386709213256836, 0.31388211250305176, 0.3139328956604004, 0.31394290924072266, 0.31396985054016113, 0.3139760494232178, 0.31403613090515137, 0.3140370845794678, 0.31406593322753906, 0.3140718936920166, 0.31409215927124023, 0.31410789489746094, 0.3141438961029053, 0.31416797637939453, 0.31417012214660645, 0.31421804428100586, 0.31423091888427734, 0.31424593925476074, 0.31433987617492676, 0.3143899440765381, 0.3143908977508545, 0.31440186500549316, 0.3144111633300781, 0.3144199848175049, 0.3144400119781494, 0.31446099281311035, 0.31447291374206543, 0.31447601318359375, 0.31450700759887695, 0.31450796127319336, 0.3145170211791992, 0.31452202796936035, 0.31452393531799316, 0.3145320415496826, 0.314532995223999, 0.314532995223999, 0.3145599365234375, 0.3146018981933594, 0.3146359920501709, 0.3146498203277588, 0.31469202041625977, 0.3147099018096924, 0.31471800804138184, 0.31471800804138184, 0.3147249221801758, 0.3147311210632324, 0.31473779678344727, 0.3147568702697754, 0.3147571086883545, 0.3147580623626709, 0.31477785110473633, 0.31478095054626465, 0.31478095054626465, 0.3147909641265869, 0.31484103202819824, 0.31485795974731445, 0.31487298011779785, 0.3148791790008545, 0.31490588188171387, 0.3149287700653076, 0.31493687629699707, 0.3149559497833252, 0.3149690628051758, 0.31499814987182617, 0.3150181770324707, 0.3150210380554199, 0.3150761127471924, 0.31508398056030273, 0.31510210037231445, 0.3151071071624756, 0.3151259422302246, 0.31514501571655273, 0.315187931060791, 0.31519603729248047, 0.3151998519897461, 0.31521105766296387, 0.3152461051940918, 0.31525683403015137, 0.3152790069580078, 0.31528210639953613, 0.31528401374816895, 0.3153228759765625, 0.31535792350769043, 0.31538915634155273, 0.31542086601257324, 0.3154771327972412, 0.3154900074005127, 0.3154919147491455, 0.31549811363220215, 0.31551408767700195, 0.31554102897644043, 0.31557512283325195, 0.3155980110168457, 0.31560802459716797, 0.3156118392944336, 0.3156249523162842, 0.31563591957092285, 0.31564903259277344, 0.31590914726257324, 0.3159630298614502, 0.31601595878601074, 0.31604599952697754, 0.3160669803619385, 0.31607604026794434, 0.31607699394226074, 0.31609082221984863, 0.3161029815673828, 0.31615185737609863, 0.31618404388427734, 0.31618499755859375, 0.31624698638916016, 0.316270112991333, 0.3162810802459717, 0.31628918647766113, 0.31630682945251465, 0.31632304191589355, 0.3163890838623047, 0.31640195846557617, 0.3164091110229492, 0.3165900707244873, 0.3166031837463379, 0.31661295890808105, 0.3166511058807373, 0.3168671131134033, 0.31688714027404785, 0.3168940544128418, 0.316910982131958, 0.316986083984375, 0.3170359134674072, 0.3170459270477295, 0.3170502185821533, 0.3170762062072754, 0.31711506843566895, 0.3171980381011963, 0.3172168731689453, 0.3172750473022461, 0.3173050880432129, 0.3173379898071289, 0.3173708915710449, 0.31741809844970703, 0.3174479007720947, 0.31745195388793945, 0.31748390197753906, 0.3174901008605957, 0.3174920082092285, 0.3177909851074219, 0.31787896156311035, 0.31798791885375977, 0.3179969787597656, 0.3180670738220215, 0.31812119483947754, 0.31812214851379395, 0.31812286376953125, 0.31821513175964355, 0.31833410263061523, 0.3183579444885254, 0.3183920383453369, 0.31843113899230957, 0.3184850215911865, 0.31884002685546875, 0.3195459842681885, 0.3204679489135742, 0.3207709789276123, 0.3208448886871338, 0.32122087478637695, 0.3212461471557617, 0.3216691017150879, 0.32298898696899414, 0.32303404808044434, 0.32346391677856445, 0.3235189914703369, 0.32358789443969727, 0.32363319396972656, 0.3236370086669922, 0.3237478733062744, 0.32375288009643555, 0.32376718521118164, 0.32377195358276367, 0.3237900733947754, 0.323793888092041, 0.32379794120788574, 0.3238399028778076, 0.3238949775695801, 0.32396388053894043, 0.3239741325378418, 0.3240079879760742, 0.3240208625793457, 0.3240361213684082, 0.324084997177124, 0.3241288661956787, 0.324185848236084, 0.324199914932251, 0.32421183586120605, 0.32425999641418457, 0.3242619037628174, 0.3242940902709961, 0.3242971897125244, 0.3243680000305176, 0.3243680000305176, 0.324390172958374, 0.3244760036468506, 0.3244950771331787, 0.32450079917907715, 0.32454919815063477, 0.3245658874511719, 0.3245999813079834, 0.32460594177246094, 0.324627161026001, 0.32464003562927246, 0.3246440887451172, 0.32467103004455566, 0.3246910572052002, 0.32473015785217285, 0.32475709915161133, 0.3247668743133545, 0.32477307319641113, 0.32477617263793945, 0.3247849941253662, 0.32479095458984375, 0.32485508918762207, 0.32486987113952637, 0.3248729705810547, 0.3248779773712158, 0.3248789310455322, 0.32487916946411133, 0.3248929977416992, 0.3249220848083496, 0.3249480724334717, 0.32495713233947754, 0.3249661922454834, 0.3249850273132324, 0.32500410079956055, 0.32503199577331543, 0.3250460624694824, 0.3250560760498047, 0.32508301734924316, 0.32509589195251465, 0.3251070976257324, 0.3251159191131592, 0.3251619338989258, 0.3251640796661377, 0.3251640796661377, 0.3251678943634033, 0.32517385482788086, 0.32517409324645996, 0.32522082328796387, 0.32524895668029785, 0.3252580165863037, 0.32526683807373047, 0.3252689838409424, 0.3252699375152588, 0.3252999782562256, 0.3253018856048584, 0.3253350257873535, 0.32538414001464844, 0.3253951072692871, 0.3253970146179199, 0.32540392875671387, 0.3254120349884033, 0.32541584968566895, 0.3254208564758301, 0.3254249095916748, 0.32543182373046875, 0.32544493675231934, 0.32544898986816406, 0.32544994354248047, 0.3254561424255371, 0.32546091079711914, 0.3254690170288086, 0.3254690170288086, 0.3254849910736084, 0.3254969120025635, 0.32550501823425293, 0.32550597190856934, 0.32552409172058105, 0.3255300521850586, 0.3255460262298584, 0.325559139251709, 0.3255729675292969, 0.3256099224090576, 0.3256099224090576, 0.32561397552490234, 0.32562804222106934, 0.32562899589538574, 0.3256669044494629, 0.3257019519805908, 0.3257129192352295, 0.3257157802581787, 0.32572007179260254, 0.32572007179260254, 0.32573699951171875, 0.3257410526275635, 0.3257448673248291, 0.32575201988220215, 0.3257560729980469, 0.32576584815979004, 0.32581496238708496, 0.32584500312805176, 0.32584595680236816, 0.32585906982421875, 0.32586002349853516, 0.32586216926574707, 0.3258810043334961, 0.3259010314941406, 0.32591795921325684, 0.32592010498046875, 0.32592201232910156, 0.3259279727935791, 0.325930118560791, 0.3259451389312744, 0.32596683502197266, 0.32596921920776367, 0.3259880542755127, 0.3260061740875244, 0.3260679244995117, 0.326092004776001, 0.3261070251464844, 0.3261089324951172, 0.3261399269104004, 0.3261418342590332, 0.32619214057922363, 0.3262021541595459, 0.3262059688568115, 0.32620882987976074, 0.32621121406555176, 0.3262350559234619, 0.32624220848083496, 0.3262641429901123, 0.32628703117370605, 0.3263089656829834, 0.326340913772583, 0.32637786865234375, 0.326383113861084, 0.32640600204467773, 0.32642507553100586, 0.3264319896697998, 0.3264341354370117, 0.32645297050476074, 0.3264751434326172, 0.32648301124572754, 0.32651686668395996, 0.3265190124511719, 0.3265259265899658, 0.32654595375061035, 0.32654690742492676, 0.32656097412109375, 0.32656407356262207, 0.3265810012817383, 0.3265841007232666, 0.32658910751342773, 0.3266129493713379, 0.3266489505767822, 0.32666993141174316, 0.3267059326171875, 0.3267190456390381, 0.32674217224121094, 0.32676005363464355, 0.3267819881439209, 0.3267960548400879, 0.3268120288848877, 0.32685112953186035, 0.32688283920288086, 0.3268859386444092, 0.3269188404083252, 0.32694411277770996, 0.32700419425964355, 0.327023983001709, 0.32704901695251465, 0.3270740509033203, 0.32707905769348145, 0.32717394828796387, 0.32719898223876953, 0.32724905014038086, 0.3272519111633301, 0.32732295989990234, 0.32733702659606934, 0.327347993850708, 0.3273658752441406, 0.3274118900299072, 0.3274710178375244, 0.32749485969543457, 0.32750391960144043, 0.32752299308776855, 0.3276338577270508, 0.3276660442352295, 0.32770681381225586, 0.3277130126953125, 0.3277699947357178, 0.3278040885925293, 0.3278799057006836, 0.32790589332580566, 0.32791996002197266, 0.3279531002044678, 0.3279531002044678, 0.3279540538787842, 0.3280031681060791, 0.32800912857055664, 0.3280158042907715, 0.3280210494995117, 0.32802796363830566, 0.3280320167541504, 0.32804298400878906, 0.3280601501464844, 0.328106164932251, 0.3281080722808838, 0.3281240463256836, 0.32816314697265625, 0.3281741142272949, 0.32822394371032715, 0.328261137008667, 0.32827305793762207, 0.32838892936706543, 0.32840895652770996, 0.32842206954956055, 0.3284339904785156, 0.32843899726867676, 0.32845401763916016, 0.3284740447998047, 0.32848405838012695, 0.32850098609924316, 0.3285410404205322, 0.3285989761352539, 0.32861900329589844, 0.3286440372467041, 0.3286581039428711, 0.32869505882263184, 0.3287220001220703, 0.3287661075592041, 0.32881808280944824, 0.3288300037384033, 0.3289651870727539, 0.32897019386291504, 0.3289778232574463, 0.3289921283721924, 0.32907700538635254, 0.3291199207305908, 0.32914209365844727, 0.3291900157928467, 0.3291940689086914, 0.3292560577392578, 0.3292968273162842, 0.32935500144958496, 0.32941484451293945, 0.3294341564178467, 0.32944202423095703, 0.32950687408447266, 0.32956385612487793, 0.32958102226257324, 0.32958102226257324, 0.32982516288757324, 0.3298830986022949, 0.3299698829650879, 0.329970121383667, 0.33017420768737793, 0.33029794692993164, 0.33051609992980957, 0.3305339813232422, 0.33069396018981934, 0.3307678699493408, 0.3309471607208252, 0.3317439556121826, 0.33208584785461426, 0.33219289779663086, 0.3329010009765625, 0.3331170082092285, 0.33402085304260254, 0.33454108238220215, 0.33458805084228516, 0.334636926651001, 0.33466601371765137, 0.3346729278564453, 0.3347740173339844, 0.3348109722137451, 0.3348240852355957, 0.33483099937438965, 0.33485889434814453, 0.33490991592407227, 0.33493995666503906, 0.3349430561065674, 0.33510279655456543, 0.33510708808898926, 0.3352169990539551, 0.3352539539337158, 0.3352789878845215, 0.3353312015533447, 0.33533596992492676, 0.3353450298309326, 0.3353850841522217, 0.33545994758605957, 0.3355109691619873, 0.33553409576416016, 0.33553600311279297, 0.33556199073791504, 0.3355898857116699, 0.33570098876953125, 0.3357090950012207, 0.33577895164489746, 0.33579397201538086, 0.3358290195465088, 0.3358938694000244, 0.3358941078186035, 0.3359100818634033, 0.33593297004699707, 0.33594489097595215, 0.3359489440917969, 0.33597898483276367, 0.33599090576171875, 0.3360099792480469, 0.33602404594421387, 0.33603787422180176, 0.33605504035949707, 0.3360888957977295, 0.33609509468078613, 0.33611202239990234, 0.33611512184143066, 0.33614206314086914, 0.33614397048950195, 0.33615803718566895, 0.33617091178894043, 0.33618688583374023, 0.3361971378326416, 0.33620500564575195, 0.33622097969055176, 0.336223840713501, 0.3362250328063965, 0.3362729549407959, 0.3362860679626465, 0.33629798889160156, 0.3363010883331299, 0.33630895614624023, 0.3363211154937744, 0.33632493019104004, 0.33634114265441895, 0.33635497093200684, 0.3363630771636963, 0.3363800048828125, 0.33639001846313477, 0.3363940715789795, 0.33642101287841797, 0.33643007278442383, 0.33647704124450684, 0.3364861011505127, 0.3364889621734619, 0.3365199565887451, 0.3365201950073242, 0.336529016494751, 0.3365628719329834, 0.3365898132324219, 0.3366110324859619, 0.33666205406188965, 0.33667588233947754, 0.33669590950012207, 0.3367037773132324, 0.33672499656677246, 0.3367469310760498, 0.336759090423584, 0.3367798328399658, 0.33678388595581055, 0.33678507804870605, 0.3368217945098877, 0.3368351459503174, 0.3368649482727051, 0.336942195892334, 0.3369450569152832, 0.33697080612182617, 0.3369710445404053, 0.3369741439819336, 0.3369748592376709, 0.3369910717010498, 0.33701586723327637, 0.33702802658081055, 0.3370330333709717, 0.33704209327697754, 0.3370490074157715, 0.3370540142059326, 0.33705806732177734, 0.33705806732177734, 0.33709216117858887, 0.33710193634033203, 0.3371121883392334, 0.33711695671081543, 0.3371250629425049, 0.3371551036834717, 0.3372170925140381, 0.33724498748779297, 0.3372499942779541, 0.337277889251709, 0.3372931480407715, 0.33730411529541016, 0.33736586570739746, 0.3373899459838867, 0.33745884895324707, 0.33748698234558105, 0.33751511573791504, 0.33751797676086426, 0.3375368118286133, 0.33754992485046387, 0.3376140594482422, 0.33765482902526855, 0.33775901794433594, 0.33782219886779785, 0.33784008026123047, 0.33788514137268066, 0.3378920555114746, 0.3379180431365967, 0.3379189968109131, 0.33795785903930664, 0.3380129337310791, 0.3380131721496582, 0.3380320072174072, 0.33811402320861816, 0.3381218910217285, 0.33812594413757324, 0.3381500244140625, 0.33815693855285645, 0.33829212188720703, 0.3383040428161621, 0.3383808135986328, 0.33838915824890137, 0.3383920192718506, 0.3384120464324951, 0.3385651111602783, 0.3386809825897217, 0.3387141227722168, 0.33876895904541016, 0.3387908935546875, 0.3388230800628662, 0.33890604972839355, 0.33890795707702637, 0.3389251232147217, 0.3389441967010498, 0.3390228748321533, 0.33902907371520996, 0.3390350341796875, 0.33925604820251465, 0.3393208980560303, 0.339339017868042, 0.33935999870300293, 0.3394050598144531, 0.33948206901550293, 0.3395068645477295, 0.33976006507873535, 0.3398890495300293, 0.3399198055267334, 0.3399200439453125, 0.33994388580322266, 0.3399648666381836, 0.34011292457580566, 0.34023308753967285, 0.3402879238128662, 0.34029603004455566, 0.34030699729919434, 0.3403201103210449, 0.3403329849243164, 0.34035396575927734, 0.34038591384887695, 0.34058380126953125, 0.3407468795776367, 0.34085607528686523, 0.34098291397094727, 0.34102606773376465, 0.34105992317199707, 0.3418290615081787, 0.3419978618621826, 0.34218502044677734, 0.34223318099975586, 0.3425600528717041, 0.34264707565307617, 0.3427848815917969, 0.3429269790649414, 0.3442718982696533, 0.34566712379455566, 0.34593701362609863, 0.3461270332336426, 0.34624290466308594, 0.3463761806488037, 0.3464322090148926, 0.3464980125427246, 0.3465840816497803, 0.34659814834594727, 0.3467400074005127, 0.346790075302124, 0.34679293632507324, 0.3468048572540283, 0.3468058109283447, 0.3468620777130127, 0.34696316719055176, 0.3469820022583008, 0.34701085090637207, 0.3470180034637451, 0.347153902053833, 0.34715819358825684, 0.3471970558166504, 0.34720301628112793, 0.3472449779510498, 0.34729599952697754, 0.34740400314331055, 0.3474619388580322, 0.3474748134613037, 0.34751391410827637, 0.34753918647766113, 0.34761691093444824, 0.3477199077606201, 0.34774184226989746, 0.34776902198791504, 0.34778690338134766, 0.34787607192993164, 0.3480110168457031, 0.3480567932128906, 0.34806203842163086, 0.3480978012084961, 0.34810495376586914, 0.3481459617614746, 0.34821009635925293, 0.34821295738220215, 0.34825801849365234, 0.34827589988708496, 0.3482980728149414, 0.34830689430236816, 0.3483729362487793, 0.3484010696411133, 0.3486979007720947, 0.34876203536987305, 0.3488490581512451, 0.34906005859375, 0.34911012649536133, 0.34915781021118164, 0.34922194480895996, 0.3492739200592041, 0.3492929935455322, 0.34935808181762695, 0.3493928909301758, 0.3495368957519531, 0.3496370315551758, 0.3497140407562256, 0.34973907470703125, 0.349794864654541, 0.3498110771179199, 0.34998297691345215, 0.35018301010131836, 0.350208044052124, 0.3502161502838135, 0.35031986236572266, 0.35062694549560547, 0.3506951332092285, 0.35086894035339355, 0.3508720397949219, 0.3513619899749756, 0.3514740467071533, 0.351794958114624, 0.3518710136413574, 0.35199809074401855, 0.3527190685272217, 0.35419201850891113, 0.35697507858276367, 0.3575899600982666, 0.35771894454956055, 0.35794615745544434, 0.35796189308166504, 0.3584442138671875, 0.35872507095336914, 0.3587958812713623, 0.35887980461120605, 0.3589930534362793, 0.3591170310974121, 0.3593580722808838, 0.3596949577331543, 0.3597290515899658, 0.3598051071166992, 0.35999083518981934, 0.3602128028869629, 0.3602328300476074, 0.3603699207305908, 0.36038804054260254, 0.360576868057251, 0.3606550693511963, 0.3607611656188965, 0.3611729145050049, 0.36121201515197754, 0.36121296882629395, 0.3621859550476074, 0.3622121810913086, 0.36228013038635254, 0.3623020648956299, 0.36272597312927246, 0.36278700828552246, 0.3628730773925781, 0.36783504486083984, 0.3687751293182373, 0.3699028491973877, 0.37021613121032715, 0.3703160285949707, 0.37044191360473633, 0.37093091011047363, 0.3717820644378662, 0.3745300769805908, 0.37552690505981445, 0.37640810012817383, 0.37726402282714844, 0.3786611557006836, 0.37964916229248047, 0.38047099113464355, 0.3806321620941162, 0.3810100555419922, 0.3811190128326416, 0.3820528984069824, 0.3821890354156494, 0.3823812007904053, 0.38274598121643066, 0.3831000328063965, 0.38385891914367676, 0.3879580497741699, 0.39013099670410156, 0.39031314849853516, 0.3904271125793457, 0.3909878730773926, 0.39127588272094727, 0.3913860321044922, 0.3914210796356201, 0.391646146774292, 0.39218592643737793, 0.392894983291626, 0.39330005645751953, 0.393341064453125, 0.3942141532897949, 0.39458489418029785, 0.3947939872741699, 0.3959531784057617, 0.3961758613586426, 0.3966240882873535, 0.39736413955688477, 0.3999519348144531, 0.40030622482299805, 0.40216898918151855, 0.4024810791015625, 0.4031810760498047, 0.40371084213256836, 0.4060049057006836, 0.4066431522369385, 0.4066641330718994, 0.407196044921875]</t>
+  </si>
+  <si>
+    <t>[0.3144681453704834, 0.3144710063934326, 0.3147871494293213, 0.3148829936981201, 0.31502699851989746, 0.31527113914489746, 0.3176000118255615, 0.3193931579589844, 0.31946706771850586, 0.32156801223754883, 0.3216969966888428, 0.32218098640441895, 0.3222990036010742, 0.32233691215515137, 0.3223421573638916, 0.3224339485168457, 0.3225409984588623, 0.32259583473205566, 0.3226041793823242, 0.32263803482055664, 0.32265281677246094, 0.32268190383911133, 0.3228311538696289, 0.3229939937591553, 0.32309412956237793, 0.32311582565307617, 0.3231627941131592, 0.3231830596923828, 0.32326602935791016, 0.3232710361480713, 0.32332491874694824, 0.32342004776000977, 0.32346487045288086, 0.3234710693359375, 0.3235809803009033, 0.32364797592163086, 0.32372307777404785, 0.3237271308898926, 0.3237600326538086, 0.32378196716308594, 0.32378387451171875, 0.32384300231933594, 0.3238680362701416, 0.3239309787750244, 0.32393598556518555, 0.32395410537719727, 0.3239760398864746, 0.32402777671813965, 0.3240349292755127, 0.3240501880645752, 0.32405614852905273, 0.32407212257385254, 0.3241410255432129, 0.32419610023498535, 0.3242759704589844, 0.324321985244751, 0.324321985244751, 0.3243288993835449, 0.3243410587310791, 0.3243889808654785, 0.32439517974853516, 0.3244149684906006, 0.3244199752807617, 0.3244309425354004, 0.3244340419769287, 0.3244450092315674, 0.3244969844818115, 0.32459092140197754, 0.3246028423309326, 0.32460498809814453, 0.32460594177246094, 0.3246641159057617, 0.3246941566467285, 0.32469606399536133, 0.3247089385986328, 0.32473182678222656, 0.32475805282592773, 0.32479310035705566, 0.3248269557952881, 0.3248460292816162, 0.3249170780181885, 0.32492494583129883, 0.3249399662017822, 0.32495594024658203, 0.32496190071105957, 0.32498717308044434, 0.3250010013580322, 0.3250291347503662, 0.3250870704650879, 0.32509803771972656, 0.325106143951416, 0.32517004013061523, 0.3252089023590088, 0.32523012161254883, 0.3253021240234375, 0.32532691955566406, 0.3253340721130371, 0.3253591060638428, 0.3253810405731201, 0.32540082931518555, 0.3254108428955078, 0.32544898986816406, 0.325451135635376, 0.3254690170288086, 0.3254880905151367, 0.32548999786376953, 0.32549190521240234, 0.3255798816680908, 0.32558202743530273, 0.3256189823150635, 0.3257009983062744, 0.32573699951171875, 0.3257460594177246, 0.3257632255554199, 0.32578492164611816, 0.3259239196777344, 0.3259727954864502, 0.32602500915527344, 0.326038122177124, 0.3260459899902344, 0.32617998123168945, 0.3262369632720947, 0.3262608051300049, 0.3262660503387451, 0.3262901306152344, 0.32630395889282227, 0.3263399600982666, 0.3263530731201172, 0.3264188766479492, 0.3264498710632324, 0.32653212547302246, 0.3269009590148926, 0.32692694664001465, 0.3269369602203369, 0.3269689083099365, 0.32709789276123047, 0.32714295387268066, 0.3271639347076416, 0.3272130489349365, 0.3272359371185303, 0.32729005813598633, 0.327502965927124, 0.32750701904296875, 0.3277420997619629, 0.32815122604370117, 0.3283090591430664, 0.32869696617126465, 0.32875514030456543, 0.3289148807525635, 0.3292520046234131, 0.3292720317840576, 0.32946205139160156, 0.32964301109313965, 0.3300139904022217, 0.3312199115753174, 0.3319530487060547, 0.33318114280700684, 0.33344388008117676, 0.33350706100463867, 0.3335399627685547, 0.3335428237915039, 0.333636999130249, 0.3336820602416992, 0.3336939811706543, 0.3337070941925049, 0.3337891101837158, 0.33391594886779785, 0.33399295806884766, 0.3340449333190918, 0.3340630531311035, 0.3340771198272705, 0.33414793014526367, 0.33420705795288086, 0.3342139720916748, 0.33422303199768066, 0.3342409133911133, 0.3342888355255127, 0.33430004119873047, 0.33434200286865234, 0.33435893058776855, 0.3344588279724121, 0.3344700336456299, 0.334475040435791, 0.33463311195373535, 0.3346409797668457, 0.3347349166870117, 0.3347959518432617, 0.33481907844543457, 0.334885835647583, 0.3348870277404785, 0.33489203453063965, 0.33489990234375, 0.33491992950439453, 0.33493781089782715, 0.33495402336120605, 0.33501505851745605, 0.33502793312072754, 0.33505916595458984, 0.33507490158081055, 0.33510589599609375, 0.3351600170135498, 0.33516693115234375, 0.33518195152282715, 0.33519697189331055, 0.3352210521697998, 0.3352320194244385, 0.3352470397949219, 0.3352499008178711, 0.3352851867675781, 0.33528804779052734, 0.3353109359741211, 0.33532094955444336, 0.33537912368774414, 0.33541393280029297, 0.3354151248931885, 0.3354167938232422, 0.3354310989379883, 0.3354370594024658, 0.33545589447021484, 0.33548593521118164, 0.33550596237182617, 0.3355088233947754, 0.3355119228363037, 0.3355569839477539, 0.3355679512023926, 0.3355691432952881, 0.33558106422424316, 0.33559393882751465, 0.33562493324279785, 0.33563804626464844, 0.3356800079345703, 0.3356809616088867, 0.33568811416625977, 0.3357279300689697, 0.33573389053344727, 0.3357369899749756, 0.33576297760009766, 0.3357691764831543, 0.33579301834106445, 0.3358180522918701, 0.33581995964050293, 0.335906982421875, 0.3359098434448242, 0.3359830379486084, 0.3360121250152588, 0.3360130786895752, 0.33602309226989746, 0.3360438346862793, 0.336047887802124, 0.3360719680786133, 0.33609890937805176, 0.33612585067749023, 0.33617115020751953, 0.3361999988555908, 0.3362081050872803, 0.3362300395965576, 0.33623814582824707, 0.3362560272216797, 0.3362569808959961, 0.3362579345703125, 0.3362710475921631, 0.33628106117248535, 0.3362879753112793, 0.33631110191345215, 0.3363218307495117, 0.33634400367736816, 0.3363630771636963, 0.33640193939208984, 0.3364431858062744, 0.3364558219909668, 0.33646416664123535, 0.3364689350128174, 0.3364901542663574, 0.33649396896362305, 0.3365209102630615, 0.3365321159362793, 0.33654117584228516, 0.33655810356140137, 0.33655881881713867, 0.3365612030029297, 0.33657407760620117, 0.3365750312805176, 0.3365750312805176, 0.3365769386291504, 0.33658885955810547, 0.3365950584411621, 0.33663105964660645, 0.336641788482666, 0.3366429805755615, 0.3366570472717285, 0.33679795265197754, 0.33679819107055664, 0.3368368148803711, 0.33684301376342773, 0.33685994148254395, 0.3368978500366211, 0.3369150161743164, 0.33693599700927734, 0.3369410037994385, 0.3369448184967041, 0.3369638919830322, 0.33699798583984375, 0.33699893951416016, 0.33699989318847656, 0.3370230197906494, 0.33704614639282227, 0.33704710006713867, 0.3370499610900879, 0.3370630741119385, 0.33707404136657715, 0.3371767997741699, 0.33717918395996094, 0.33719801902770996, 0.3372030258178711, 0.33720993995666504, 0.33724403381347656, 0.33725500106811523, 0.33727097511291504, 0.3372931480407715, 0.3372957706451416, 0.33730101585388184, 0.3373110294342041, 0.3373379707336426, 0.3373830318450928, 0.3374011516571045, 0.33740997314453125, 0.33742809295654297, 0.337446928024292, 0.33750319480895996, 0.3375370502471924, 0.3375518321990967, 0.3375558853149414, 0.33756303787231445, 0.33759498596191406, 0.33765316009521484, 0.33766889572143555, 0.3376779556274414, 0.33768796920776367, 0.3377089500427246, 0.337738037109375, 0.33774900436401367, 0.3377509117126465, 0.33782505989074707, 0.3378479480743408, 0.33789896965026855, 0.3379030227661133, 0.33794116973876953, 0.33794307708740234, 0.33803510665893555, 0.33803892135620117, 0.3380420207977295, 0.3381052017211914, 0.3381218910217285, 0.3381340503692627, 0.3381950855255127, 0.33823108673095703, 0.33824801445007324, 0.3382740020751953, 0.3383450508117676, 0.3383519649505615, 0.3383522033691406, 0.3384120464324951, 0.33852386474609375, 0.3386039733886719, 0.338623046875, 0.33875489234924316, 0.33878517150878906, 0.3388049602508545, 0.3389451503753662, 0.33895015716552734, 0.3390829563140869, 0.33913111686706543, 0.3392000198364258, 0.33922600746154785, 0.339339017868042, 0.3393740653991699, 0.3394160270690918, 0.33943700790405273, 0.3397221565246582, 0.33984804153442383, 0.3399631977081299, 0.33999204635620117, 0.340101957321167, 0.3404519557952881, 0.34047889709472656, 0.34065699577331543, 0.3413410186767578, 0.3415508270263672, 0.3415870666503906, 0.34204888343811035, 0.3423278331756592, 0.34233999252319336, 0.3424818515777588, 0.34267687797546387, 0.34392881393432617, 0.3441178798675537, 0.344357967376709, 0.3444991111755371, 0.3445301055908203, 0.3447999954223633, 0.34484291076660156, 0.34487009048461914, 0.34511804580688477, 0.34511899948120117, 0.3452129364013672, 0.3452770709991455, 0.34528589248657227, 0.34530091285705566, 0.3453090190887451, 0.34534692764282227, 0.3453528881072998, 0.34540295600891113, 0.34543800354003906, 0.34548091888427734, 0.34552502632141113, 0.345628023147583, 0.3456840515136719, 0.34570908546447754, 0.34571099281311035, 0.34577202796936035, 0.34578514099121094, 0.3458099365234375, 0.345930814743042, 0.3460071086883545, 0.34603190422058105, 0.3460659980773926, 0.3460729122161865, 0.34607386589050293, 0.3461170196533203, 0.3461179733276367, 0.34613704681396484, 0.34613919258117676, 0.3461730480194092, 0.34618401527404785, 0.34627580642700195, 0.34627795219421387, 0.346311092376709, 0.34633898735046387, 0.3463399410247803, 0.3463399410247803, 0.34636998176574707, 0.3463718891143799, 0.3463761806488037, 0.34638404846191406, 0.3463919162750244, 0.3463938236236572, 0.3464510440826416, 0.3464779853820801, 0.3465149402618408, 0.3465549945831299, 0.34656500816345215, 0.3465728759765625, 0.3465900421142578, 0.3466019630432129, 0.34661412239074707, 0.34662818908691406, 0.3466329574584961, 0.34664201736450195, 0.34665703773498535, 0.34665703773498535, 0.34666895866394043, 0.3466758728027344, 0.3466830253601074, 0.34670400619506836, 0.34671497344970703, 0.3467419147491455, 0.3467559814453125, 0.34676098823547363, 0.3467679023742676, 0.3467700481414795, 0.3467710018157959, 0.3468048572540283, 0.34682512283325195, 0.3468360900878906, 0.34683990478515625, 0.3468480110168457, 0.3468759059906006, 0.34689998626708984, 0.3469099998474121, 0.34691500663757324, 0.34693217277526855, 0.34697794914245605, 0.34698009490966797, 0.3469851016998291, 0.3469860553741455, 0.34700608253479004, 0.34700703620910645, 0.34702086448669434, 0.34702610969543457, 0.3470439910888672, 0.3470439910888672, 0.3470449447631836, 0.3470799922943115, 0.34713006019592285, 0.34714508056640625, 0.34714603424072266, 0.34719300270080566, 0.3471968173980713, 0.3472280502319336, 0.3472299575805664, 0.3472461700439453, 0.3472468852996826, 0.34725308418273926, 0.34725499153137207, 0.3472719192504883, 0.3472750186920166, 0.3472769260406494, 0.34728002548217773, 0.3472869396209717, 0.3472881317138672, 0.34732794761657715, 0.34734296798706055, 0.3473639488220215, 0.34737610816955566, 0.3473799228668213, 0.34738612174987793, 0.34738612174987793, 0.34741711616516113, 0.34745192527770996, 0.34746384620666504, 0.3474719524383545, 0.34748196601867676, 0.347491979598999, 0.34750819206237793, 0.347520112991333, 0.34752607345581055, 0.34752702713012695, 0.34752893447875977, 0.34752988815307617, 0.34754204750061035, 0.34755396842956543, 0.34755802154541016, 0.3475639820098877, 0.34757280349731445, 0.34759998321533203, 0.3476099967956543, 0.3476121425628662, 0.34761691093444824, 0.34763479232788086, 0.3476378917694092, 0.3476579189300537, 0.3476748466491699, 0.34768009185791016, 0.3476870059967041, 0.3476879596710205, 0.3477180004119873, 0.34772706031799316, 0.34772801399230957, 0.34775590896606445, 0.34777188301086426, 0.3477790355682373, 0.3478090763092041, 0.34781789779663086, 0.3478579521179199, 0.347869873046875, 0.34787821769714355, 0.3479001522064209, 0.34790897369384766, 0.34791111946105957, 0.3479180335998535, 0.3479349613189697, 0.34793519973754883, 0.34793901443481445, 0.34795403480529785, 0.34795403480529785, 0.3479630947113037, 0.3479728698730469, 0.34799981117248535, 0.3480050563812256, 0.3480088710784912, 0.3480110168457031, 0.34801197052001953, 0.34801316261291504, 0.34802699089050293, 0.3480360507965088, 0.348038911819458, 0.34804797172546387, 0.3480658531188965, 0.34807515144348145, 0.3480842113494873, 0.3480851650238037, 0.3480851650238037, 0.34810805320739746, 0.3481111526489258, 0.3481111526489258, 0.3481159210205078, 0.3481180667877197, 0.3481180667877197, 0.34811997413635254, 0.34812021255493164, 0.34812092781066895, 0.3481321334838867, 0.34814000129699707, 0.3481459617614746, 0.34814906120300293, 0.3481600284576416, 0.34816503524780273, 0.34816503524780273, 0.3481760025024414, 0.3481872081756592, 0.34819889068603516, 0.3482089042663574, 0.34824180603027344, 0.3482530117034912, 0.3482639789581299, 0.3482680320739746, 0.348268985748291, 0.34827208518981934, 0.3482780456542969, 0.34828996658325195, 0.34830188751220703, 0.3483121395111084, 0.34833383560180664, 0.3483400344848633, 0.3483409881591797, 0.3483419418334961, 0.34834790229797363, 0.34835219383239746, 0.3483569622039795, 0.348369836807251, 0.34838199615478516, 0.3483870029449463, 0.34839296340942383, 0.34839296340942383, 0.34839701652526855, 0.34842705726623535, 0.34842991828918457, 0.3484461307525635, 0.34847497940063477, 0.3485221862792969, 0.34855008125305176, 0.3485720157623291, 0.3485729694366455, 0.34857702255249023, 0.3485898971557617, 0.3486020565032959, 0.34863805770874023, 0.34866905212402344, 0.34868288040161133, 0.34868812561035156, 0.34870195388793945, 0.3487269878387451, 0.3487558364868164, 0.34876108169555664, 0.34879207611083984, 0.3488030433654785, 0.34882283210754395, 0.3488290309906006, 0.34884190559387207, 0.3488810062408447, 0.3489260673522949, 0.34892892837524414, 0.3489360809326172, 0.34895896911621094, 0.3489658832550049, 0.34897685050964355, 0.3489871025085449, 0.3489987850189209, 0.3490030765533447, 0.34900498390197754, 0.34900999069213867, 0.34900999069213867, 0.349027156829834, 0.3490331172943115, 0.34904980659484863, 0.34905195236206055, 0.34905385971069336, 0.34905409812927246, 0.3491220474243164, 0.34914207458496094, 0.3491520881652832, 0.34915900230407715, 0.34916210174560547, 0.3491640090942383, 0.3491661548614502, 0.34917688369750977, 0.3492090702056885, 0.3492431640625, 0.34926581382751465, 0.34928202629089355, 0.349290132522583, 0.3493080139160156, 0.3493227958679199, 0.34932398796081543, 0.34939098358154297, 0.34940099716186523, 0.3494589328765869, 0.349484920501709, 0.34957003593444824, 0.34958577156066895, 0.3496260643005371, 0.3496549129486084, 0.34966206550598145, 0.34967494010925293, 0.34967803955078125, 0.3497200012207031, 0.34972286224365234, 0.34972381591796875, 0.34972500801086426, 0.34972715377807617, 0.34991002082824707, 0.349977970123291, 0.3499898910522461, 0.3500099182128906, 0.35004711151123047, 0.35017991065979004, 0.35018396377563477, 0.35022711753845215, 0.3502388000488281, 0.35024404525756836, 0.3502810001373291, 0.35031604766845703, 0.3503248691558838, 0.3503739833831787, 0.35040712356567383, 0.3504190444946289, 0.3504459857940674, 0.3504509925842285, 0.3505730628967285, 0.35058116912841797, 0.35059690475463867, 0.35070204734802246, 0.3507351875305176, 0.35076284408569336, 0.35077691078186035, 0.350844144821167, 0.3509359359741211, 0.35095787048339844, 0.35095882415771484, 0.3510110378265381, 0.3511509895324707, 0.35115909576416016, 0.3512420654296875, 0.3512539863586426, 0.3512609004974365, 0.35137295722961426, 0.3514399528503418, 0.35146093368530273, 0.351668119430542, 0.35173797607421875, 0.35201597213745117, 0.3521449565887451, 0.35227203369140625, 0.352294921875, 0.35255002975463867, 0.3526601791381836, 0.3528261184692383, 0.35292506217956543, 0.3529820442199707, 0.35312914848327637, 0.3533968925476074, 0.353726863861084, 0.35402512550354004, 0.35410404205322266, 0.3542788028717041, 0.3545098304748535, 0.3560168743133545, 0.35631680488586426, 0.3564779758453369, 0.3565030097961426, 0.35651588439941406, 0.3565249443054199, 0.35665011405944824, 0.35680294036865234, 0.3569338321685791, 0.3570709228515625, 0.3570990562438965, 0.3572089672088623, 0.3573310375213623, 0.35738301277160645, 0.3575170040130615, 0.35753417015075684, 0.35761117935180664, 0.3576200008392334, 0.3576319217681885, 0.3576622009277344, 0.35773801803588867, 0.3578369617462158, 0.3579859733581543, 0.3580451011657715, 0.3580780029296875, 0.3581390380859375, 0.35814905166625977, 0.3581569194793701, 0.3581869602203369, 0.35823488235473633, 0.3582770824432373, 0.35831117630004883, 0.35831785202026367, 0.3583230972290039, 0.3583378791809082, 0.3584098815917969, 0.3584260940551758, 0.35846400260925293, 0.35852503776550293, 0.3585641384124756, 0.35860705375671387, 0.3586418628692627, 0.3587770462036133, 0.35880398750305176, 0.3588449954986572, 0.35885000228881836, 0.35885119438171387, 0.3588900566101074, 0.3590891361236572, 0.35913991928100586, 0.3591878414154053, 0.3591949939727783, 0.3592510223388672, 0.3592660427093506, 0.35932087898254395, 0.35950708389282227, 0.3595619201660156, 0.359576940536499, 0.3596329689025879, 0.359652042388916, 0.3596689701080322, 0.3597378730773926, 0.359860897064209, 0.35987305641174316, 0.35988903045654297, 0.3599069118499756, 0.3599209785461426, 0.3599400520324707, 0.35996007919311523, 0.35996508598327637, 0.3600008487701416, 0.3600349426269531, 0.3600800037384033, 0.3601229190826416, 0.3601419925689697, 0.36017513275146484, 0.3601951599121094, 0.3602139949798584, 0.3603169918060303, 0.3603200912475586, 0.3603248596191406, 0.3603661060333252, 0.3603789806365967, 0.36043310165405273, 0.360461950302124, 0.36049795150756836, 0.3605031967163086, 0.360645055770874, 0.3609910011291504, 0.3609941005706787, 0.36105895042419434, 0.3610801696777344, 0.361083984375, 0.36108899116516113, 0.3612661361694336, 0.36127591133117676, 0.3612959384918213, 0.36134815216064453, 0.3614189624786377, 0.3615601062774658, 0.36157894134521484, 0.36166906356811523, 0.3617250919342041, 0.3618319034576416, 0.3620600700378418, 0.36222290992736816, 0.3624131679534912, 0.3624250888824463, 0.3625807762145996, 0.36298108100891113, 0.3635079860687256, 0.36406803131103516, 0.3640890121459961, 0.36423587799072266, 0.3643350601196289, 0.36487913131713867, 0.3664131164550781, 0.36685800552368164, 0.367095947265625, 0.3673129081726074, 0.36829590797424316, 0.36839890480041504, 0.36849188804626465, 0.36854100227355957, 0.3686251640319824, 0.36934804916381836, 0.3693840503692627, 0.36949706077575684, 0.3695061206817627, 0.3696920871734619, 0.3699038028717041, 0.37039899826049805, 0.37055087089538574, 0.3706951141357422, 0.3707101345062256, 0.37088799476623535, 0.3709869384765625, 0.3711881637573242, 0.37151408195495605, 0.3715169429779053, 0.3715240955352783, 0.37168002128601074, 0.3720419406890869, 0.3721129894256592, 0.37219691276550293, 0.37220096588134766, 0.3728599548339844, 0.3735811710357666, 0.3736298084259033, 0.37380194664001465, 0.3739149570465088, 0.3743579387664795, 0.3747100830078125, 0.3749730587005615, 0.377918004989624, 0.3786020278930664, 0.3786790370941162, 0.379410982131958, 0.37954115867614746, 0.37961792945861816, 0.37964296340942383, 0.3798508644104004, 0.3802299499511719, 0.3803219795227051, 0.3809640407562256, 0.3810610771179199, 0.3820629119873047, 0.38452696800231934, 0.38475704193115234, 0.38573694229125977, 0.3860619068145752, 0.3863558769226074, 0.3864009380340576, 0.3875260353088379, 0.3901381492614746, 0.3902461528778076, 0.3904280662536621, 0.3904449939727783, 0.390484094619751, 0.39090800285339355, 0.39102697372436523, 0.3910338878631592, 0.39107704162597656, 0.39168691635131836, 0.3920719623565674, 0.3922908306121826, 0.392366886138916, 0.39263081550598145, 0.39330291748046875, 0.39342284202575684, 0.3939061164855957, 0.3950498104095459, 0.3965489864349365, 0.3968379497528076, 0.4000260829925537, 0.40053582191467285, 0.40069007873535156, 0.40085506439208984, 0.4012179374694824, 0.40131497383117676, 0.4013180732727051, 0.4014110565185547, 0.4015309810638428, 0.4016098976135254, 0.40186190605163574, 0.40250086784362793, 0.4025731086730957, 0.4025919437408447, 0.40262413024902344, 0.4027729034423828, 0.4027879238128662, 0.4029099941253662, 0.4043550491333008, 0.4047119617462158, 0.40531492233276367, 0.4068288803100586, 0.4074220657348633, 0.4081599712371826, 0.40848612785339355, 0.4084951877593994, 0.41178202629089355, 0.41324496269226074, 0.4135549068450928, 0.4137728214263916]</t>
+  </si>
+  <si>
+    <t>[0.24349403381347656, 0.24353814125061035, 0.24358820915222168, 0.24371814727783203, 0.24380111694335938, 0.24382615089416504, 0.24388504028320312, 0.24391508102416992, 0.24391794204711914, 0.24399590492248535, 0.24402904510498047, 0.24410295486450195, 0.24412298202514648, 0.2441270351409912, 0.24414396286010742, 0.2441868782043457, 0.24419617652893066, 0.24427199363708496, 0.24428391456604004, 0.2443249225616455, 0.24442815780639648, 0.2444288730621338, 0.2444918155670166, 0.24450898170471191, 0.24452686309814453, 0.2445361614227295, 0.24460482597351074, 0.24460697174072266, 0.24460911750793457, 0.24467182159423828, 0.24469685554504395, 0.24472498893737793, 0.2447679042816162, 0.24484896659851074, 0.24485993385314941, 0.24487900733947754, 0.2449791431427002, 0.2449939250946045, 0.24501800537109375, 0.24503707885742188, 0.24512505531311035, 0.2452530860900879, 0.24527406692504883, 0.24528789520263672, 0.24533796310424805, 0.2453460693359375, 0.2454700469970703, 0.24547982215881348, 0.2455000877380371, 0.24560904502868652, 0.24561405181884766, 0.24564409255981445, 0.24567604064941406, 0.24569487571716309, 0.24571895599365234, 0.2458021640777588, 0.24591803550720215, 0.2459259033203125, 0.24593400955200195, 0.24600887298583984, 0.24606800079345703, 0.2461109161376953, 0.24611210823059082, 0.24613618850708008, 0.24618816375732422, 0.24619793891906738, 0.24636292457580566, 0.2464292049407959, 0.24643683433532715, 0.24646806716918945, 0.24646997451782227, 0.24666190147399902, 0.24680495262145996, 0.24685096740722656, 0.2469019889831543, 0.24691390991210938, 0.24702906608581543, 0.24738597869873047, 0.24756979942321777, 0.24765396118164062, 0.24775409698486328, 0.24788880348205566, 0.24794578552246094, 0.24805784225463867, 0.248337984085083, 0.24861907958984375, 0.24949002265930176, 0.25020313262939453, 0.25162601470947266, 0.25174593925476074, 0.2528400421142578, 0.2531008720397949, 0.2532529830932617, 0.25351691246032715, 0.25368499755859375, 0.25374913215637207, 0.25378990173339844, 0.25386595726013184, 0.25389885902404785, 0.253925085067749, 0.2539808750152588, 0.25399303436279297, 0.2540750503540039, 0.2541038990020752, 0.25411009788513184, 0.25415611267089844, 0.2541971206665039, 0.2542150020599365, 0.25430989265441895, 0.2543320655822754, 0.25436902046203613, 0.2543830871582031, 0.2544209957122803, 0.25443506240844727, 0.2544820308685303, 0.2545008659362793, 0.25455212593078613, 0.2545590400695801, 0.2545609474182129, 0.2545638084411621, 0.2545771598815918, 0.2545928955078125, 0.25460386276245117, 0.25461411476135254, 0.25461697578430176, 0.2546250820159912, 0.2546257972717285, 0.25463414192199707, 0.2546670436859131, 0.25469303131103516, 0.25470805168151855, 0.25472187995910645, 0.25472402572631836, 0.25477004051208496, 0.2547891139984131, 0.2547941207885742, 0.25480103492736816, 0.2548060417175293, 0.2548179626464844, 0.2548220157623291, 0.2548489570617676, 0.25486207008361816, 0.2548668384552002, 0.2548840045928955, 0.2548949718475342, 0.2549009323120117, 0.2549021244049072, 0.25490689277648926, 0.25490689277648926, 0.25490808486938477, 0.2549118995666504, 0.25496983528137207, 0.2549779415130615, 0.25500988960266113, 0.255018949508667, 0.25502490997314453, 0.25502514839172363, 0.25503110885620117, 0.2550342082977295, 0.25504207611083984, 0.2550489902496338, 0.25505495071411133, 0.25505995750427246, 0.2550678253173828, 0.25510191917419434, 0.25510406494140625, 0.2551109790802002, 0.2551150321960449, 0.2551259994506836, 0.25515317916870117, 0.25516796112060547, 0.2551710605621338, 0.25519299507141113, 0.25519800186157227, 0.25519895553588867, 0.2552030086517334, 0.2552180290222168, 0.2552199363708496, 0.25522589683532715, 0.25522804260253906, 0.255234956741333, 0.2552487850189209, 0.2552671432495117, 0.255267858505249, 0.25527000427246094, 0.2552909851074219, 0.2552940845489502, 0.25530505180358887, 0.2553129196166992, 0.255328893661499, 0.25533008575439453, 0.25533294677734375, 0.2553420066833496, 0.25534605979919434, 0.25534701347351074, 0.25534701347351074, 0.2553520202636719, 0.2553548812866211, 0.25536489486694336, 0.2553679943084717, 0.2553718090057373, 0.25539183616638184, 0.25539708137512207, 0.2553980350494385, 0.2554030418395996, 0.255403995513916, 0.25541210174560547, 0.2554149627685547, 0.2554290294647217, 0.25545382499694824, 0.25545406341552734, 0.25546789169311523, 0.2554759979248047, 0.2554771900177002, 0.2554800510406494, 0.25548696517944336, 0.2554969787597656, 0.25550389289855957, 0.2555069923400879, 0.2555229663848877, 0.25552892684936523, 0.2555429935455322, 0.2555520534515381, 0.25556015968322754, 0.25556302070617676, 0.2555689811706543, 0.25557589530944824, 0.25560784339904785, 0.25560879707336426, 0.25560903549194336, 0.2556130886077881, 0.2556180953979492, 0.25562095642089844, 0.25563788414001465, 0.25565409660339355, 0.2556591033935547, 0.2556650638580322, 0.25568604469299316, 0.2556920051574707, 0.2557029724121094, 0.2557108402252197, 0.25571489334106445, 0.2557220458984375, 0.2557229995727539, 0.2557339668273926, 0.2557401657104492, 0.25574398040771484, 0.25576186180114746, 0.25576210021972656, 0.25577306747436523, 0.25577497482299805, 0.25577807426452637, 0.2557790279388428, 0.25578904151916504, 0.25579404830932617, 0.2557969093322754, 0.2558021545410156, 0.25580310821533203, 0.2558138370513916, 0.2558250427246094, 0.2558259963989258, 0.25583600997924805, 0.25586700439453125, 0.25586795806884766, 0.25587010383605957, 0.2558729648590088, 0.25589585304260254, 0.2559170722961426, 0.25592589378356934, 0.25592708587646484, 0.255932092666626, 0.25594615936279297, 0.25595903396606445, 0.2559628486633301, 0.25597691535949707, 0.2559819221496582, 0.2559847831726074, 0.2559850215911865, 0.25600695610046387, 0.256026029586792, 0.256026029586792, 0.2560269832611084, 0.2560300827026367, 0.256040096282959, 0.25606298446655273, 0.2560689449310303, 0.256072998046875, 0.25608015060424805, 0.25609898567199707, 0.2561008930206299, 0.2561028003692627, 0.25610804557800293, 0.25610899925231934, 0.2561359405517578, 0.25614309310913086, 0.25614500045776367, 0.25615501403808594, 0.2561650276184082, 0.2561759948730469, 0.2561769485473633, 0.2561910152435303, 0.25620102882385254, 0.25621581077575684, 0.25621795654296875, 0.2562270164489746, 0.25623416900634766, 0.2562439441680908, 0.25624799728393555, 0.25624990463256836, 0.25627899169921875, 0.2562839984893799, 0.256289005279541, 0.256317138671875, 0.25632500648498535, 0.25632715225219727, 0.256328821182251, 0.2563350200653076, 0.2563459873199463, 0.2563600540161133, 0.2563607692718506, 0.25637292861938477, 0.2563750743865967, 0.2563819885253906, 0.2564070224761963, 0.2564241886138916, 0.2564260959625244, 0.2564280033111572, 0.256436824798584, 0.256450891494751, 0.2564730644226074, 0.25649189949035645, 0.2565147876739502, 0.2565181255340576, 0.25652289390563965, 0.2565310001373291, 0.25653910636901855, 0.25653982162475586, 0.2565460205078125, 0.25661492347717285, 0.25661706924438477, 0.2566249370574951, 0.25662994384765625, 0.25664210319519043, 0.25664687156677246, 0.25664687156677246, 0.2566511631011963, 0.2566530704498291, 0.25666213035583496, 0.25667905807495117, 0.25672006607055664, 0.2567329406738281, 0.25673604011535645, 0.256760835647583, 0.2567708492279053, 0.2567939758300781, 0.2568049430847168, 0.2568089962005615, 0.2568199634552002, 0.25682616233825684, 0.25685906410217285, 0.2568662166595459, 0.2569141387939453, 0.25691795349121094, 0.25695300102233887, 0.25695300102233887, 0.25696897506713867, 0.25698184967041016, 0.25698399543762207, 0.2569868564605713, 0.25699520111083984, 0.257004976272583, 0.25701093673706055, 0.2570228576660156, 0.25705814361572266, 0.25707578659057617, 0.25708508491516113, 0.2570919990539551, 0.25711607933044434, 0.25715208053588867, 0.25717687606811523, 0.257188081741333, 0.25719499588012695, 0.2572190761566162, 0.2572669982910156, 0.2573521137237549, 0.2573530673980713, 0.2573680877685547, 0.25739598274230957, 0.25742006301879883, 0.2574310302734375, 0.2574319839477539, 0.25744199752807617, 0.2574610710144043, 0.25747203826904297, 0.2575080394744873, 0.2575111389160156, 0.2575540542602539, 0.25759387016296387, 0.2576870918273926, 0.25771307945251465, 0.2577340602874756, 0.25777602195739746, 0.2579009532928467, 0.2579030990600586, 0.25795698165893555, 0.2579669952392578, 0.25801587104797363, 0.25802087783813477, 0.2581460475921631, 0.25820088386535645, 0.25821423530578613, 0.25823378562927246, 0.2582390308380127, 0.2582509517669678, 0.25834012031555176, 0.2584528923034668, 0.2584829330444336, 0.25849103927612305, 0.2584998607635498, 0.2585289478302002, 0.2586081027984619, 0.25872206687927246, 0.25908493995666504, 0.25922489166259766, 0.25943899154663086, 0.259584903717041, 0.25963497161865234, 0.2597031593322754, 0.25978994369506836, 0.2600381374359131, 0.2601180076599121, 0.2604668140411377, 0.26063990592956543, 0.26227712631225586, 0.2624778747558594, 0.26395702362060547, 0.2640538215637207, 0.2641730308532715, 0.2644507884979248, 0.26448988914489746, 0.26459598541259766, 0.2647120952606201, 0.26471900939941406, 0.2647240161895752, 0.26477885246276855, 0.26488685607910156, 0.264923095703125, 0.2649409770965576, 0.26494383811950684, 0.2650120258331299, 0.2651050090789795, 0.26517486572265625, 0.2653348445892334, 0.2653510570526123, 0.2653989791870117, 0.2654390335083008, 0.2654690742492676, 0.2654759883880615, 0.26548099517822266, 0.2655022144317627, 0.2655150890350342, 0.2655520439147949, 0.26557087898254395, 0.2655761241912842, 0.2655789852142334, 0.2655792236328125, 0.26558589935302734, 0.2656059265136719, 0.2656221389770508, 0.2656240463256836, 0.2656269073486328, 0.26563096046447754, 0.26563096046447754, 0.26564812660217285, 0.2656698226928711, 0.2656710147857666, 0.265671968460083, 0.26569294929504395, 0.2656979560852051, 0.2656979560852051, 0.2657029628753662, 0.2657029628753662, 0.26572608947753906, 0.26574087142944336, 0.2657470703125, 0.26575398445129395, 0.26575398445129395, 0.2657811641693115, 0.2657918930053711, 0.2657938003540039, 0.2658109664916992, 0.26582980155944824, 0.265855073928833, 0.2658660411834717, 0.26587414741516113, 0.26589298248291016, 0.2658967971801758, 0.26590800285339355, 0.26590895652770996, 0.2659270763397217, 0.2659299373626709, 0.2659580707550049, 0.2659628391265869, 0.2659780979156494, 0.2659788131713867, 0.26598310470581055, 0.2660081386566162, 0.26602792739868164, 0.26603078842163086, 0.2660489082336426, 0.2660701274871826, 0.26608991622924805, 0.2660961151123047, 0.2660980224609375, 0.2661130428314209, 0.2661139965057373, 0.2661550045013428, 0.2661559581756592, 0.2661571502685547, 0.26616406440734863, 0.2661750316619873, 0.2661921977996826, 0.26619601249694824, 0.2662019729614258, 0.2662169933319092, 0.2662489414215088, 0.26629185676574707, 0.2663300037384033, 0.2663559913635254, 0.2663600444793701, 0.26639699935913086, 0.2664010524749756, 0.26641297340393066, 0.2664158344268799, 0.2664158344268799, 0.2664601802825928, 0.26647305488586426, 0.266495943069458, 0.26650500297546387, 0.2665247917175293, 0.2665538787841797, 0.2665691375732422, 0.26657986640930176, 0.2665839195251465, 0.2666189670562744, 0.26662516593933105, 0.2666280269622803, 0.26667189598083496, 0.2666749954223633, 0.26670002937316895, 0.26671290397644043, 0.2667210102081299, 0.2667219638824463, 0.2667350769042969, 0.26677584648132324, 0.2667808532714844, 0.2667820453643799, 0.26679110527038574, 0.26679396629333496, 0.26679396629333496, 0.2667968273162842, 0.2667980194091797, 0.2668130397796631, 0.266826868057251, 0.26683592796325684, 0.26683688163757324, 0.26684093475341797, 0.26685094833374023, 0.26685214042663574, 0.2668590545654297, 0.2668631076812744, 0.2668731212615967, 0.26689815521240234, 0.2669079303741455, 0.26694393157958984, 0.26697301864624023, 0.2669799327850342, 0.2669849395751953, 0.26700878143310547, 0.26703500747680664, 0.26705408096313477, 0.26705408096313477, 0.2670609951019287, 0.2670729160308838, 0.2670779228210449, 0.26708006858825684, 0.2670929431915283, 0.2670931816101074, 0.26712608337402344, 0.2671630382537842, 0.2671809196472168, 0.2672269344329834, 0.2672538757324219, 0.2672569751739502, 0.26726484298706055, 0.2672719955444336, 0.2672860622406006, 0.2672889232635498, 0.26731181144714355, 0.2673759460449219, 0.2674100399017334, 0.2674121856689453, 0.26743412017822266, 0.2674431800842285, 0.2674679756164551, 0.2674729824066162, 0.2674860954284668, 0.26749300956726074, 0.267503023147583, 0.26754212379455566, 0.2675740718841553, 0.2676210403442383, 0.2676248550415039, 0.267650842666626, 0.2676830291748047, 0.26770806312561035, 0.2677152156829834, 0.26773786544799805, 0.2677619457244873, 0.26781702041625977, 0.26781797409057617, 0.26784801483154297, 0.2678568363189697, 0.26787590980529785, 0.26787710189819336, 0.26790285110473633, 0.26791810989379883, 0.26791906356811523, 0.2679309844970703, 0.26794004440307617, 0.26795196533203125, 0.2679629325866699, 0.26796507835388184, 0.2679710388183594, 0.2679760456085205, 0.2680189609527588, 0.2680518627166748, 0.2680799961090088, 0.2680840492248535, 0.26818084716796875, 0.26821208000183105, 0.2682158946990967, 0.26824092864990234, 0.26827001571655273, 0.26832103729248047, 0.26833009719848633, 0.26833605766296387, 0.26836109161376953, 0.26837706565856934, 0.26839685440063477, 0.26842689514160156, 0.2684328556060791, 0.2684900760650635, 0.26854801177978516, 0.2685558795928955, 0.26860904693603516, 0.2686278820037842, 0.2686309814453125, 0.2686741352081299, 0.2686891555786133, 0.26872706413269043, 0.26880908012390137, 0.26888585090637207, 0.2689180374145508, 0.2690160274505615, 0.26905012130737305, 0.26905202865600586, 0.2690708637237549, 0.26919007301330566, 0.26920104026794434, 0.2692258358001709, 0.2692298889160156, 0.2692890167236328, 0.2693319320678711, 0.2693629264831543, 0.26938891410827637, 0.2695341110229492, 0.26958513259887695, 0.26959705352783203, 0.26961803436279297, 0.2696411609649658, 0.2697470188140869, 0.26982593536376953, 0.26982784271240234, 0.2699291706085205, 0.2699730396270752, 0.27001500129699707, 0.27003908157348633, 0.2701590061187744, 0.2705848217010498, 0.270784854888916, 0.2708249092102051, 0.27096009254455566, 0.27100300788879395, 0.2713899612426758, 0.2726140022277832, 0.27271008491516113, 0.27460503578186035, 0.2746272087097168, 0.27468204498291016, 0.2751030921936035, 0.275501012802124, 0.27572107315063477, 0.2757291793823242, 0.27579307556152344, 0.27580690383911133, 0.27582597732543945, 0.2758309841156006, 0.2758328914642334, 0.2758920192718506, 0.2759249210357666, 0.2759580612182617, 0.27597594261169434, 0.2761359214782715, 0.2762410640716553, 0.276263952255249, 0.27633094787597656, 0.27634620666503906, 0.2763991355895996, 0.27643680572509766, 0.2765040397644043, 0.2765209674835205, 0.2765522003173828, 0.27658700942993164, 0.27658987045288086, 0.27661705017089844, 0.27661705017089844, 0.27662014961242676, 0.2766439914703369, 0.27669811248779297, 0.2767159938812256, 0.27672290802001953, 0.27672815322875977, 0.2767479419708252, 0.2768089771270752, 0.27681493759155273, 0.2768259048461914, 0.27697014808654785, 0.27702808380126953, 0.27704906463623047, 0.2770500183105469, 0.2770998477935791, 0.27713704109191895, 0.27715206146240234, 0.27715516090393066, 0.27716588973999023, 0.2772200107574463, 0.2772989273071289, 0.27730607986450195, 0.27730894088745117, 0.27730894088745117, 0.27731895446777344, 0.27738094329833984, 0.27739500999450684, 0.2774059772491455, 0.2774159908294678, 0.27745890617370605, 0.2774980068206787, 0.27750205993652344, 0.27752089500427246, 0.2775440216064453, 0.27755093574523926, 0.27761101722717285, 0.2776200771331787, 0.27762794494628906, 0.27764415740966797, 0.27765989303588867, 0.2776620388031006, 0.27768802642822266, 0.27768898010253906, 0.27776408195495605, 0.27777910232543945, 0.2777988910675049, 0.27784013748168945, 0.27784109115600586, 0.27784299850463867, 0.2778449058532715, 0.27786707878112793, 0.2779049873352051, 0.27792906761169434, 0.2780029773712158, 0.27803993225097656, 0.27803993225097656, 0.2780721187591553, 0.27811598777770996, 0.2781388759613037, 0.2782299518585205, 0.27828311920166016, 0.27833104133605957, 0.2783660888671875, 0.27837586402893066, 0.27838611602783203, 0.27844810485839844, 0.27846407890319824, 0.2785170078277588, 0.27852702140808105, 0.27864599227905273, 0.27866697311401367, 0.278698205947876, 0.2788970470428467, 0.2789430618286133, 0.27895402908325195, 0.2790231704711914, 0.2791271209716797, 0.27913808822631836, 0.2792050838470459, 0.2792689800262451, 0.27932310104370117, 0.2793281078338623, 0.2793409824371338, 0.2793419361114502, 0.27934980392456055, 0.27935791015625, 0.27945590019226074, 0.2795238494873047, 0.27953290939331055, 0.2795419692993164, 0.27957797050476074, 0.27957987785339355, 0.27959489822387695, 0.2796919345855713, 0.2800729274749756, 0.28061604499816895, 0.2807199954986572, 0.2808670997619629, 0.28099608421325684, 0.28129100799560547, 0.28168797492980957, 0.28192687034606934, 0.2826681137084961, 0.2850039005279541, 0.2872428894042969, 0.2879948616027832, 0.28818416595458984, 0.288769006729126, 0.2888619899749756, 0.28896403312683105, 0.2891111373901367, 0.28911495208740234, 0.2891981601715088, 0.28972411155700684, 0.2897379398345947, 0.2897520065307617, 0.2898280620574951, 0.28995609283447266, 0.2899911403656006, 0.29001688957214355, 0.29013586044311523, 0.29022717475891113, 0.2903878688812256, 0.2905750274658203, 0.29057908058166504, 0.2905871868133545, 0.29075121879577637, 0.2908320426940918, 0.29083800315856934, 0.2910609245300293, 0.29152393341064453, 0.29160189628601074, 0.29161906242370605, 0.2920699119567871, 0.2920989990234375, 0.29212403297424316, 0.2921450138092041, 0.29261302947998047, 0.2926449775695801, 0.29276490211486816, 0.29302501678466797, 0.29369401931762695, 0.29375410079956055, 0.2984349727630615, 0.29850292205810547, 0.2986259460449219, 0.29870104789733887, 0.29918479919433594, 0.2994709014892578, 0.2995891571044922, 0.2998020648956299, 0.29995298385620117, 0.3000059127807617, 0.3002970218658447, 0.30031800270080566, 0.3004629611968994, 0.3005080223083496, 0.3005359172821045, 0.300537109375, 0.30066394805908203, 0.3006758689880371, 0.30077290534973145, 0.3008110523223877, 0.30083203315734863, 0.300915002822876, 0.3009660243988037, 0.30100107192993164, 0.3012228012084961, 0.3013739585876465, 0.3016321659088135, 0.3019580841064453, 0.30211400985717773, 0.30220890045166016, 0.3022279739379883, 0.30239415168762207, 0.3027670383453369, 0.3030118942260742, 0.30303215980529785, 0.3035571575164795, 0.3036210536956787, 0.3081979751586914, 0.3092358112335205, 0.3095269203186035, 0.3103799819946289, 0.3104100227355957, 0.31081700325012207, 0.31090497970581055, 0.3110508918762207, 0.3113429546356201, 0.31148219108581543, 0.3114910125732422, 0.31151485443115234, 0.3116950988769531, 0.3117189407348633, 0.3118760585784912, 0.3119068145751953, 0.31206583976745605, 0.3121678829193115, 0.31224894523620605, 0.3122830390930176, 0.3124549388885498, 0.3124721050262451, 0.3124818801879883, 0.3126389980316162, 0.3127248287200928, 0.3127310276031494, 0.31281495094299316, 0.3136119842529297, 0.31562113761901855, 0.32263994216918945, 0.32665586471557617, 0.3266780376434326, 0.3271310329437256, 0.32747793197631836, 0.32784008979797363, 0.32784414291381836, 0.3281550407409668, 0.3282480239868164, 0.3290219306945801, 0.33144402503967285, 0.33187222480773926, 0.3331019878387451, 0.3335230350494385, 0.3342750072479248, 0.3347349166870117, 0.33545398712158203, 0.3359968662261963, 0.33721494674682617, 0.33757591247558594, 0.33889293670654297, 0.3389749526977539, 0.33901405334472656, 0.3393831253051758, 0.3395419120788574, 0.33979010581970215, 0.3409090042114258, 0.3410310745239258, 0.34151482582092285, 0.3430781364440918, 0.34372782707214355, 0.34458088874816895, 0.34494590759277344, 0.3459911346435547, 0.34600400924682617, 0.34752798080444336, 0.34758806228637695, 0.34983015060424805, 0.3508450984954834, 0.35109686851501465, 0.35262203216552734, 0.3557090759277344, 0.35660409927368164, 0.3569159507751465]</t>
+  </si>
+  <si>
+    <t>[0.29155898094177246, 0.29232096672058105, 0.292496919631958, 0.2976260185241699, 0.29779911041259766, 0.2984650135040283, 0.29853296279907227, 0.2985548973083496, 0.2985999584197998, 0.29869818687438965, 0.29881715774536133, 0.29888105392456055, 0.29892396926879883, 0.2991018295288086, 0.2991211414337158, 0.2992229461669922, 0.29929113388061523, 0.29933786392211914, 0.2993459701538086, 0.2995011806488037, 0.29950904846191406, 0.29991888999938965, 0.3000807762145996, 0.3000969886779785, 0.30016613006591797, 0.30017995834350586, 0.30027008056640625, 0.3003699779510498, 0.30042386054992676, 0.300429105758667, 0.3004450798034668, 0.30046606063842773, 0.3005061149597168, 0.3007071018218994, 0.30076098442077637, 0.3007681369781494, 0.30078697204589844, 0.30079102516174316, 0.3008410930633545, 0.3008911609649658, 0.30107808113098145, 0.30113911628723145, 0.30116796493530273, 0.30119800567626953, 0.3012092113494873, 0.30124807357788086, 0.3013429641723633, 0.30136680603027344, 0.30137085914611816, 0.30139780044555664, 0.3014249801635742, 0.3014998435974121, 0.3015139102935791, 0.3015248775482178, 0.30153584480285645, 0.30157899856567383, 0.3016209602355957, 0.30168581008911133, 0.3017079830169678, 0.3017590045928955, 0.30176305770874023, 0.3017871379852295, 0.301846981048584, 0.30188894271850586, 0.30191898345947266, 0.30192089080810547, 0.30196309089660645, 0.30199599266052246, 0.3020198345184326, 0.3020288944244385, 0.30209994316101074, 0.3021280765533447, 0.3021738529205322, 0.30222105979919434, 0.30223989486694336, 0.30229806900024414, 0.30231285095214844, 0.3023519515991211, 0.30236196517944336, 0.3024260997772217, 0.3024730682373047, 0.30248093605041504, 0.3025181293487549, 0.3025379180908203, 0.3026309013366699, 0.30263209342956543, 0.302685022354126, 0.3027839660644531, 0.3027989864349365, 0.30292701721191406, 0.3030118942260742, 0.3030660152435303, 0.3031270503997803, 0.3032381534576416, 0.3033311367034912, 0.3033909797668457, 0.3035149574279785, 0.30367517471313477, 0.3037400245666504, 0.3037879467010498, 0.30454206466674805, 0.30517005920410156, 0.3078629970550537, 0.3081820011138916, 0.3083348274230957, 0.30854320526123047, 0.30855393409729004, 0.30867695808410645, 0.30909109115600586, 0.30918216705322266, 0.30927109718322754, 0.3092830181121826, 0.30931687355041504, 0.3093740940093994, 0.3093900680541992, 0.30940914154052734, 0.3095409870147705, 0.3095669746398926, 0.30958080291748047, 0.30963587760925293, 0.3096427917480469, 0.30971789360046387, 0.3097400665283203, 0.30974292755126953, 0.30975794792175293, 0.30989789962768555, 0.30991506576538086, 0.309920072555542, 0.3099381923675537, 0.31000494956970215, 0.3100597858428955, 0.3101339340209961, 0.3101499080657959, 0.31018590927124023, 0.310269832611084, 0.31032586097717285, 0.31037306785583496, 0.31040406227111816, 0.3104119300842285, 0.31046009063720703, 0.31046199798583984, 0.31047821044921875, 0.31049203872680664, 0.31063294410705566, 0.3106358051300049, 0.3107428550720215, 0.31075286865234375, 0.3108060359954834, 0.3108189105987549, 0.31083202362060547, 0.31087279319763184, 0.3108818531036377, 0.3108839988708496, 0.310884952545166, 0.31093883514404297, 0.31095194816589355, 0.31100988388061523, 0.3110191822052002, 0.3110339641571045, 0.311053991317749, 0.3110928535461426, 0.3111238479614258, 0.3111271858215332, 0.3111450672149658, 0.31116509437561035, 0.31122303009033203, 0.3112671375274658, 0.31126904487609863, 0.3112819194793701, 0.31128501892089844, 0.3113081455230713, 0.3113088607788086, 0.3113260269165039, 0.31134891510009766, 0.3114941120147705, 0.3114969730377197, 0.31149888038635254, 0.3115229606628418, 0.31152892112731934, 0.31153202056884766, 0.31153297424316406, 0.311582088470459, 0.31158995628356934, 0.31168198585510254, 0.31170201301574707, 0.3117029666900635, 0.3117189407348633, 0.3117339611053467, 0.31179213523864746, 0.3118128776550293, 0.3118138313293457, 0.3118269443511963, 0.31183290481567383, 0.31183505058288574, 0.31186580657958984, 0.3119070529937744, 0.31191301345825195, 0.3119161128997803, 0.3119950294494629, 0.3120448589324951, 0.31208205223083496, 0.3120849132537842, 0.3121020793914795, 0.31215810775756836, 0.31217384338378906, 0.31218886375427246, 0.31220102310180664, 0.3122060298919678, 0.3122379779815674, 0.3122720718383789, 0.3122889995574951, 0.3122899532318115, 0.3122999668121338, 0.31230902671813965, 0.3123128414154053, 0.31233692169189453, 0.31235408782958984, 0.3123910427093506, 0.3124220371246338, 0.31242799758911133, 0.31242990493774414, 0.3124539852142334, 0.3125028610229492, 0.3125138282775879, 0.31253910064697266, 0.312546968460083, 0.3125782012939453, 0.3125789165496826, 0.31258606910705566, 0.31260204315185547, 0.3126029968261719, 0.3126029968261719, 0.31261706352233887, 0.3126211166381836, 0.3126261234283447, 0.3126668930053711, 0.3126718997955322, 0.31267809867858887, 0.31270503997802734, 0.31270599365234375, 0.31272315979003906, 0.3127279281616211, 0.3127419948577881, 0.31277990341186523, 0.3127870559692383, 0.312791109085083, 0.3127930164337158, 0.3127939701080322, 0.3127939701080322, 0.3128061294555664, 0.31281113624572754, 0.31284093856811523, 0.31285810470581055, 0.3128788471221924, 0.3129000663757324, 0.3129098415374756, 0.31292009353637695, 0.3129270076751709, 0.31293416023254395, 0.3129429817199707, 0.31294703483581543, 0.3129618167877197, 0.3129708766937256, 0.3129918575286865, 0.31299614906311035, 0.3130190372467041, 0.3130199909210205, 0.31302404403686523, 0.3130300045013428, 0.31306910514831543, 0.3130769729614258, 0.3130788803100586, 0.3130800724029541, 0.3130989074707031, 0.31310391426086426, 0.3131098747253418, 0.31313300132751465, 0.31314587593078613, 0.31316399574279785, 0.31316614151000977, 0.31317591667175293, 0.3131859302520752, 0.31319117546081543, 0.31322216987609863, 0.3132319450378418, 0.3132340908050537, 0.31328892707824707, 0.3132939338684082, 0.313309907913208, 0.3133230209350586, 0.31332898139953613, 0.3133578300476074, 0.31336402893066406, 0.3133690357208252, 0.3134119510650635, 0.3134119510650635, 0.313431978225708, 0.31345200538635254, 0.3134598731994629, 0.3134639263153076, 0.31347107887268066, 0.3134739398956299, 0.3134958744049072, 0.3135199546813965, 0.3135380744934082, 0.31354212760925293, 0.313554048538208, 0.3135650157928467, 0.31357407569885254, 0.31357908248901367, 0.31358909606933594, 0.313601016998291, 0.31371498107910156, 0.3137199878692627, 0.31373095512390137, 0.3137381076812744, 0.3137550354003906, 0.31375813484191895, 0.3137929439544678, 0.31382298469543457, 0.3138301372528076, 0.31384801864624023, 0.3138551712036133, 0.3138740062713623, 0.3139510154724121, 0.31395792961120605, 0.31398892402648926, 0.3140108585357666, 0.3140389919281006, 0.3140568733215332, 0.31413912773132324, 0.31416916847229004, 0.3141779899597168, 0.3142049312591553, 0.31421899795532227, 0.3142518997192383, 0.31426405906677246, 0.3143808841705322, 0.3144209384918213, 0.31444501876831055, 0.31444501876831055, 0.3144500255584717, 0.3144800662994385, 0.31450486183166504, 0.3145568370819092, 0.31464409828186035, 0.31484007835388184, 0.31492018699645996, 0.31494903564453125, 0.3150157928466797, 0.3152031898498535, 0.3152139186859131, 0.3153219223022461, 0.31551408767700195, 0.3155941963195801, 0.31600117683410645, 0.3161349296569824, 0.31619906425476074, 0.31658506393432617, 0.3168148994445801, 0.3172569274902344, 0.3180270195007324, 0.3190460205078125, 0.3191111087799072, 0.31918883323669434, 0.31930994987487793, 0.3193669319152832, 0.31944990158081055, 0.31951308250427246, 0.31964993476867676, 0.31972789764404297, 0.320220947265625, 0.32027101516723633, 0.32030582427978516, 0.3203902244567871, 0.3204920291900635, 0.32050204277038574, 0.3206019401550293, 0.3207058906555176, 0.3207359313964844, 0.32080698013305664, 0.32080793380737305, 0.32083606719970703, 0.32083988189697266, 0.32085394859313965, 0.3209259510040283, 0.3209409713745117, 0.3210010528564453, 0.32100415229797363, 0.32100605964660645, 0.3210139274597168, 0.32102179527282715, 0.321044921875, 0.3210868835449219, 0.3210899829864502, 0.3211231231689453, 0.32120299339294434, 0.32120513916015625, 0.321213960647583, 0.3212430477142334, 0.3212590217590332, 0.3212599754333496, 0.3212859630584717, 0.32129812240600586, 0.32138919830322266, 0.3214390277862549, 0.3214390277862549, 0.3215160369873047, 0.321519136428833, 0.3215360641479492, 0.3215510845184326, 0.3215599060058594, 0.32158803939819336, 0.32161903381347656, 0.32163190841674805, 0.32163500785827637, 0.3216359615325928, 0.3216371536254883, 0.3216409683227539, 0.32166004180908203, 0.3216872215270996, 0.3217029571533203, 0.3218519687652588, 0.3218650817871094, 0.32190680503845215, 0.32192301750183105, 0.32195496559143066, 0.3219718933105469, 0.3219928741455078, 0.32199597358703613, 0.32199788093566895, 0.32201290130615234, 0.32212090492248535, 0.32213306427001953, 0.3221700191497803, 0.3221859931945801, 0.32220983505249023, 0.32224106788635254, 0.32227301597595215, 0.32227492332458496, 0.32232093811035156, 0.32233595848083496, 0.3223400115966797, 0.3223710060119629, 0.32238197326660156, 0.32247209548950195, 0.32247400283813477, 0.322512149810791, 0.32251715660095215, 0.32252001762390137, 0.3225440979003906, 0.3225581645965576, 0.32259297370910645, 0.32259416580200195, 0.3226029872894287, 0.3226051330566406, 0.3226289749145508, 0.32264018058776855, 0.32275891304016113, 0.32277393341064453, 0.32277393341064453, 0.32286691665649414, 0.32286906242370605, 0.3229079246520996, 0.32292604446411133, 0.32298803329467773, 0.32302093505859375, 0.32303500175476074, 0.32307982444763184, 0.3230910301208496, 0.3231081962585449, 0.3231170177459717, 0.32312703132629395, 0.3231339454650879, 0.32314491271972656, 0.32317590713500977, 0.3231809139251709, 0.323253870010376, 0.3233349323272705, 0.3233509063720703, 0.3233621120452881, 0.32336997985839844, 0.32337093353271484, 0.3233938217163086, 0.3233950138092041, 0.32339906692504883, 0.3234109878540039, 0.3234140872955322, 0.323422908782959, 0.3234291076660156, 0.3234422206878662, 0.3234438896179199, 0.3234539031982422, 0.3234891891479492, 0.323498010635376, 0.3234989643096924, 0.3235280513763428, 0.3235359191894531, 0.32353782653808594, 0.3235588073730469, 0.3235640525817871, 0.32357096672058105, 0.32358288764953613, 0.32358598709106445, 0.3235960006713867, 0.32360410690307617, 0.3236351013183594, 0.3236358165740967, 0.3236391544342041, 0.32364797592163086, 0.3236510753631592, 0.3236961364746094, 0.3237030506134033, 0.32370901107788086, 0.3237309455871582, 0.3237330913543701, 0.32375597953796387, 0.32376790046691895, 0.32377004623413086, 0.3237929344177246, 0.32381582260131836, 0.323822021484375, 0.323836088180542, 0.3238410949707031, 0.3238539695739746, 0.323868989944458, 0.3238840103149414, 0.32388806343078613, 0.32390499114990234, 0.3239130973815918, 0.3239250183105469, 0.3239290714263916, 0.32396817207336426, 0.3239741325378418, 0.32399916648864746, 0.3240199089050293, 0.32404613494873047, 0.3240499496459961, 0.3240621089935303, 0.3240690231323242, 0.32407402992248535, 0.3240950107574463, 0.32412290573120117, 0.32413196563720703, 0.3241450786590576, 0.3241589069366455, 0.3241868019104004, 0.32421302795410156, 0.32422304153442383, 0.3242349624633789, 0.32423901557922363, 0.3242509365081787, 0.3242521286010742, 0.32428598403930664, 0.32429981231689453, 0.3243110179901123, 0.32431602478027344, 0.32433414459228516, 0.32434892654418945, 0.32436490058898926, 0.3243739604949951, 0.32438111305236816, 0.32439494132995605, 0.3244059085845947, 0.3244152069091797, 0.32442188262939453, 0.32442593574523926, 0.3244590759277344, 0.3244800567626953, 0.3244800567626953, 0.3244819641113281, 0.32448410987854004, 0.3244900703430176, 0.32449793815612793, 0.32449889183044434, 0.32451605796813965, 0.3245220184326172, 0.32453012466430664, 0.32457995414733887, 0.3245961666107178, 0.3246140480041504, 0.3246591091156006, 0.3246591091156006, 0.3246769905090332, 0.32468485832214355, 0.32474493980407715, 0.3247520923614502, 0.32475781440734863, 0.32477903366088867, 0.3247859477996826, 0.32482004165649414, 0.3248291015625, 0.324843168258667, 0.3248939514160156, 0.3249340057373047, 0.3249380588531494, 0.32494401931762695, 0.3249490261077881, 0.32496094703674316, 0.3249680995941162, 0.3249778747558594, 0.3249998092651367, 0.32500386238098145, 0.3250160217285156, 0.32502293586730957, 0.3250401020050049, 0.3250908851623535, 0.32509589195251465, 0.32509899139404297, 0.3251340389251709, 0.3251349925994873, 0.32521510124206543, 0.32525205612182617, 0.3252530097961426, 0.3252589702606201, 0.3252990245819092, 0.3253610134124756, 0.32540202140808105, 0.3254060745239258, 0.3254249095916748, 0.32544898986816406, 0.32546091079711914, 0.3255620002746582, 0.3256111145019531, 0.3256211280822754, 0.3256947994232178, 0.32570815086364746, 0.32578206062316895, 0.32579708099365234, 0.32586097717285156, 0.32593297958374023, 0.32597899436950684, 0.32605481147766113, 0.3261091709136963, 0.32623291015625, 0.3262619972229004, 0.32628512382507324, 0.32646799087524414, 0.3265380859375, 0.3266158103942871, 0.32666587829589844, 0.32675600051879883, 0.3268320560455322, 0.32705092430114746, 0.3271479606628418, 0.32733583450317383, 0.32735395431518555, 0.3274240493774414, 0.32760000228881836, 0.3281888961791992, 0.3290379047393799, 0.3290867805480957, 0.3298978805541992, 0.33075404167175293, 0.330935001373291, 0.33103394508361816, 0.3312389850616455, 0.3312561511993408, 0.33130788803100586, 0.33147501945495605, 0.3315269947052002, 0.33155393600463867, 0.33158302307128906, 0.3316628932952881, 0.33170008659362793, 0.33170413970947266, 0.3317129611968994, 0.3317279815673828, 0.3317551612854004, 0.33179807662963867, 0.33188700675964355, 0.3318960666656494, 0.33190107345581055, 0.33191514015197754, 0.33202099800109863, 0.332042932510376, 0.3321559429168701, 0.3321800231933594, 0.3322489261627197, 0.33226895332336426, 0.33228015899658203, 0.3323068618774414, 0.3323178291320801, 0.3323230743408203, 0.33242201805114746, 0.33245205879211426, 0.3324618339538574, 0.3325228691101074, 0.3325920104980469, 0.3325939178466797, 0.3326249122619629, 0.33263087272644043, 0.3326900005340576, 0.33274197578430176, 0.3327658176422119, 0.3327960968017578, 0.3327980041503906, 0.33279895782470703, 0.33281612396240234, 0.3328578472137451, 0.33295702934265137, 0.33297300338745117, 0.3330059051513672, 0.33303093910217285, 0.3331429958343506, 0.333233118057251, 0.333251953125, 0.33327388763427734, 0.3333930969238281, 0.33344507217407227, 0.3334829807281494, 0.3335580825805664, 0.3335590362548828, 0.33358287811279297, 0.33362412452697754, 0.3336350917816162, 0.33365893363952637, 0.33372998237609863, 0.33373498916625977, 0.333773136138916, 0.33381009101867676, 0.3338968753814697, 0.33390021324157715, 0.3339040279388428, 0.33391523361206055, 0.3339228630065918, 0.333939790725708, 0.3339681625366211, 0.3339860439300537, 0.3340291976928711, 0.33405613899230957, 0.3340599536895752, 0.3340787887573242, 0.334108829498291, 0.3341219425201416, 0.3341238498687744, 0.3341491222381592, 0.33415699005126953, 0.3341670036315918, 0.33417201042175293, 0.3341841697692871, 0.3341991901397705, 0.3342020511627197, 0.3342299461364746, 0.33426403999328613, 0.33426809310913086, 0.3342721462249756, 0.3342740535736084, 0.3342750072479248, 0.3343620300292969, 0.3343689441680908, 0.3343930244445801, 0.3343968391418457, 0.3343989849090576, 0.334399938583374, 0.3344109058380127, 0.3344130516052246, 0.33443593978881836, 0.3344409465789795, 0.33444714546203613, 0.3345320224761963, 0.33454394340515137, 0.3345451354980469, 0.3345510959625244, 0.33455896377563477, 0.3346090316772461, 0.3346569538116455, 0.3346691131591797, 0.3346719741821289, 0.3346891403198242, 0.33469390869140625, 0.33475399017333984, 0.3347811698913574, 0.33478307723999023, 0.334791898727417, 0.3347921371459961, 0.3347949981689453, 0.3348269462585449, 0.3348519802093506, 0.3348729610443115, 0.3348851203918457, 0.3349001407623291, 0.3349161148071289, 0.3349418640136719, 0.3349428176879883, 0.33499908447265625, 0.3350539207458496, 0.3350698947906494, 0.33507490158081055, 0.3350799083709717, 0.3350968360900879, 0.33511996269226074, 0.3351268768310547, 0.33513498306274414, 0.3351471424102783, 0.3351621627807617, 0.33516597747802734, 0.33516907691955566, 0.33518505096435547, 0.33518505096435547, 0.33521509170532227, 0.3352370262145996, 0.33527088165283203, 0.33530211448669434, 0.33531713485717773, 0.33533382415771484, 0.33536505699157715, 0.3354299068450928, 0.3354458808898926, 0.33545994758605957, 0.3354768753051758, 0.3354971408843994, 0.33555006980895996, 0.3355569839477539, 0.33559298515319824, 0.3355989456176758, 0.33562612533569336, 0.33571600914001465, 0.335752010345459, 0.335770845413208, 0.33581089973449707, 0.3358180522918701, 0.3358728885650635, 0.3358910083770752, 0.335906982421875, 0.33595800399780273, 0.33599114418029785, 0.33605504035949707, 0.3360929489135742, 0.33609604835510254, 0.33610010147094727, 0.33611583709716797, 0.33618783950805664, 0.3361959457397461, 0.336259126663208, 0.3362770080566406, 0.3363149166107178, 0.336529016494751, 0.3367180824279785, 0.33673906326293945, 0.33687400817871094, 0.33690404891967773, 0.33695483207702637, 0.33698296546936035, 0.3371090888977051, 0.33713698387145996, 0.33719301223754883, 0.33733415603637695, 0.3374481201171875, 0.337460994720459, 0.3379390239715576, 0.3379800319671631, 0.3384859561920166, 0.33888697624206543, 0.34079790115356445, 0.34105515480041504, 0.3417019844055176, 0.3424539566040039, 0.34258198738098145, 0.3426220417022705, 0.3426339626312256, 0.343109130859375, 0.3431520462036133, 0.3434460163116455, 0.34352803230285645, 0.3435549736022949, 0.34357404708862305, 0.34388017654418945, 0.3442227840423584, 0.34433507919311523, 0.3444340229034424, 0.3444640636444092, 0.3445727825164795, 0.34457993507385254, 0.34473705291748047, 0.3451271057128906, 0.3452320098876953, 0.3453080654144287, 0.3453238010406494, 0.3453330993652344, 0.3454289436340332, 0.34546995162963867, 0.3455519676208496, 0.3455839157104492, 0.3456418514251709, 0.3457009792327881, 0.34577107429504395, 0.3457779884338379, 0.34580397605895996, 0.3458268642425537, 0.345897912979126, 0.34592103958129883, 0.34594202041625977, 0.3460569381713867, 0.3460578918457031, 0.3462221622467041, 0.34627604484558105, 0.34632301330566406, 0.3463630676269531, 0.34642910957336426, 0.3464350700378418, 0.3464999198913574, 0.346513032913208, 0.34654903411865234, 0.3466339111328125, 0.3467369079589844, 0.34674906730651855, 0.3467888832092285, 0.3468501567840576, 0.34691500663757324, 0.3469250202178955, 0.34708595275878906, 0.34712696075439453, 0.3471670150756836, 0.3471989631652832, 0.3473351001739502, 0.34734416007995605, 0.34736204147338867, 0.3474268913269043, 0.3474609851837158, 0.3474900722503662, 0.34784698486328125, 0.347912073135376, 0.3479161262512207, 0.3479290008544922, 0.3479321002960205, 0.34803199768066406, 0.3480489253997803, 0.34876513481140137, 0.3494851589202881, 0.35349607467651367, 0.3541390895843506, 0.355072021484375, 0.35564684867858887, 0.35636186599731445, 0.3578970432281494, 0.35882091522216797, 0.35949206352233887, 0.3665468692779541, 0.367171049118042, 0.3685328960418701, 0.3820381164550781, 0.3877730369567871, 0.3883030414581299, 0.3916800022125244, 0.3935739994049072, 0.3938579559326172, 0.39450716972351074, 0.3955259323120117, 0.3981821537017822, 0.39868783950805664, 0.3988311290740967, 0.40041494369506836, 0.4009890556335449, 0.40355610847473145, 0.40503907203674316, 0.4053220748901367, 0.40572595596313477, 0.4059898853302002, 0.406857967376709, 0.40978312492370605, 0.41031408309936523, 0.41105198860168457, 0.4111149311065674, 0.4114570617675781, 0.4117569923400879, 0.41231417655944824, 0.412337064743042, 0.4129059314727783, 0.414003849029541, 0.4144120216369629, 0.41519784927368164, 0.41602516174316406, 0.4191930294036865, 0.41985011100769043, 0.42023706436157227, 0.42193102836608887, 0.4220280647277832, 0.42273688316345215, 0.42327213287353516]</t>
+  </si>
+  <si>
+    <t>[0.31191205978393555, 0.31197094917297363, 0.312122106552124, 0.3121929168701172, 0.312424898147583, 0.31292200088500977, 0.31343793869018555, 0.31992101669311523, 0.3200039863586426, 0.3202321529388428, 0.32030510902404785, 0.3204169273376465, 0.3204917907714844, 0.3205130100250244, 0.32056093215942383, 0.32061100006103516, 0.3206818103790283, 0.3206820487976074, 0.3207261562347412, 0.32090306282043457, 0.32112908363342285, 0.3212578296661377, 0.3212730884552002, 0.32132887840270996, 0.32133007049560547, 0.32136106491088867, 0.32137393951416016, 0.321378231048584, 0.3213808536529541, 0.32138800621032715, 0.32140517234802246, 0.3214070796966553, 0.32144784927368164, 0.32146191596984863, 0.32146596908569336, 0.3214750289916992, 0.3215029239654541, 0.3215160369873047, 0.32155680656433105, 0.32157206535339355, 0.3217439651489258, 0.3217439651489258, 0.3217909336090088, 0.3217930793762207, 0.3218419551849365, 0.3218669891357422, 0.3219180107116699, 0.3219180107116699, 0.32192397117614746, 0.3219478130340576, 0.32196903228759766, 0.32199788093566895, 0.32201099395751953, 0.3220388889312744, 0.3220641613006592, 0.3220791816711426, 0.32208991050720215, 0.3221011161804199, 0.3221089839935303, 0.32212090492248535, 0.32212400436401367, 0.3221409320831299, 0.3221430778503418, 0.32216310501098633, 0.3221700191497803, 0.3222041130065918, 0.32221508026123047, 0.32222890853881836, 0.3222618103027344, 0.3222651481628418, 0.3222959041595459, 0.322314977645874, 0.3223459720611572, 0.3223609924316406, 0.32236695289611816, 0.32237887382507324, 0.3223860263824463, 0.3224320411682129, 0.32245588302612305, 0.3224809169769287, 0.3224818706512451, 0.3224928379058838, 0.32249999046325684, 0.3225100040435791, 0.3225119113922119, 0.32253003120422363, 0.322551965713501, 0.3225541114807129, 0.3225579261779785, 0.32255983352661133, 0.3225841522216797, 0.32262206077575684, 0.3226299285888672, 0.32263612747192383, 0.3226449489593506, 0.32268691062927246, 0.32269287109375, 0.32271909713745117, 0.32273006439208984, 0.3227570056915283, 0.3227701187133789, 0.32277798652648926, 0.3227870464324951, 0.3228027820587158, 0.32282400131225586, 0.32283997535705566, 0.3228480815887451, 0.32286500930786133, 0.32289910316467285, 0.3229091167449951, 0.32291388511657715, 0.322965145111084, 0.32300806045532227, 0.3230311870574951, 0.32303810119628906, 0.32305097579956055, 0.3230879306793213, 0.32309603691101074, 0.32311010360717773, 0.32311081886291504, 0.3231179714202881, 0.3231220245361328, 0.3231239318847656, 0.32312893867492676, 0.3231499195098877, 0.3231630325317383, 0.3231661319732666, 0.3231799602508545, 0.32318782806396484, 0.32318806648254395, 0.32321906089782715, 0.3232250213623047, 0.32323193550109863, 0.32326292991638184, 0.3232901096343994, 0.3233020305633545, 0.32332515716552734, 0.32332801818847656, 0.32337212562561035, 0.32338714599609375, 0.32340192794799805, 0.32340216636657715, 0.3234438896179199, 0.3234720230102539, 0.3234729766845703, 0.32348012924194336, 0.32350897789001465, 0.323530912399292, 0.32354283332824707, 0.3235609531402588, 0.32357096672058105, 0.32361698150634766, 0.3236520290374756, 0.3236560821533203, 0.3236691951751709, 0.3237040042877197, 0.32371091842651367, 0.323714017868042, 0.32372307777404785, 0.32373499870300293, 0.3237490653991699, 0.3237597942352295, 0.32376694679260254, 0.3237919807434082, 0.32379603385925293, 0.3238348960876465, 0.323840856552124, 0.32384490966796875, 0.3239262104034424, 0.3239288330078125, 0.323958158493042, 0.3239610195159912, 0.32396388053894043, 0.32397007942199707, 0.32398200035095215, 0.3239929676055908, 0.32399487495422363, 0.3240349292755127, 0.32403993606567383, 0.3240668773651123, 0.3240699768066406, 0.324077844619751, 0.3240799903869629, 0.32408595085144043, 0.32408690452575684, 0.3241159915924072, 0.3241560459136963, 0.3241729736328125, 0.3241860866546631, 0.3242020606994629, 0.3242161273956299, 0.3242189884185791, 0.3242628574371338, 0.3242800235748291, 0.32428598403930664, 0.32428908348083496, 0.3243091106414795, 0.3243141174316406, 0.32431912422180176, 0.32432007789611816, 0.3243389129638672, 0.32434701919555664, 0.32436180114746094, 0.3243699073791504, 0.3243710994720459, 0.32440185546875, 0.32442307472229004, 0.32442402839660645, 0.32442688941955566, 0.3244459629058838, 0.3244750499725342, 0.32448291778564453, 0.3244941234588623, 0.3245110511779785, 0.32451915740966797, 0.3245410919189453, 0.3245429992675781, 0.324552059173584, 0.32460713386535645, 0.32464599609375, 0.32465291023254395, 0.32471203804016113, 0.32472896575927734, 0.32477784156799316, 0.3248178958892822, 0.32482194900512695, 0.32484912872314453, 0.3248729705810547, 0.3249058723449707, 0.32492899894714355, 0.3249349594116211, 0.32497215270996094, 0.3250269889831543, 0.3250601291656494, 0.3250701427459717, 0.32508015632629395, 0.32508087158203125, 0.32511019706726074, 0.3251760005950928, 0.3252100944519043, 0.3252739906311035, 0.3253910541534424, 0.3253960609436035, 0.3254580497741699, 0.32550692558288574, 0.32553815841674805, 0.3255789279937744, 0.3255808353424072, 0.325639009475708, 0.32579708099365234, 0.32599711418151855, 0.32618212699890137, 0.3261990547180176, 0.32624292373657227, 0.32626891136169434, 0.3263528347015381, 0.3266901969909668, 0.32694005966186523, 0.3279750347137451, 0.3281550407409668, 0.3309929370880127, 0.33123111724853516, 0.3312520980834961, 0.33146119117736816, 0.3317830562591553, 0.33179187774658203, 0.33184313774108887, 0.331895112991333, 0.33190202713012695, 0.33194708824157715, 0.33196187019348145, 0.3319680690765381, 0.33199405670166016, 0.3320281505584717, 0.3320629596710205, 0.3320729732513428, 0.33208298683166504, 0.33211612701416016, 0.3321819305419922, 0.3321869373321533, 0.3321959972381592, 0.3322157859802246, 0.33222293853759766, 0.33222413063049316, 0.3322629928588867, 0.33226490020751953, 0.33226704597473145, 0.3322749137878418, 0.3323190212249756, 0.3323228359222412, 0.33233094215393066, 0.3323519229888916, 0.3323519229888916, 0.3323709964752197, 0.33237314224243164, 0.33237504959106445, 0.33240604400634766, 0.3324110507965088, 0.3324141502380371, 0.33243513107299805, 0.33243703842163086, 0.33248114585876465, 0.33249902725219727, 0.3325018882751465, 0.33252406120300293, 0.3325521945953369, 0.33256006240844727, 0.33258700370788574, 0.33258914947509766, 0.3325929641723633, 0.33262014389038086, 0.33262205123901367, 0.33266615867614746, 0.3326737880706787, 0.33267807960510254, 0.33269309997558594, 0.33274102210998535, 0.3327641487121582, 0.3327648639678955, 0.33277201652526855, 0.3327820301055908, 0.33278703689575195, 0.3328127861022949, 0.332852840423584, 0.3328821659088135, 0.3329029083251953, 0.33290791511535645, 0.33292603492736816, 0.33293700218200684, 0.33298707008361816, 0.3329949378967285, 0.33301210403442383, 0.33301591873168945, 0.33304691314697266, 0.3330540657043457, 0.3330540657043457, 0.3330550193786621, 0.3330559730529785, 0.3330562114715576, 0.3330650329589844, 0.3330721855163574, 0.3330810070037842, 0.3330879211425781, 0.33309197425842285, 0.33309197425842285, 0.33309221267700195, 0.3330991268157959, 0.3331179618835449, 0.33312201499938965, 0.33312487602233887, 0.3331320285797119, 0.33315491676330566, 0.3331608772277832, 0.3331890106201172, 0.3331928253173828, 0.3331930637359619, 0.33319711685180664, 0.33320093154907227, 0.3332240581512451, 0.3332479000091553, 0.333251953125, 0.3332560062408447, 0.33327412605285645, 0.33330392837524414, 0.33331298828125, 0.33332395553588867, 0.33333706855773926, 0.3333549499511719, 0.3333618640899658, 0.33336400985717773, 0.3333709239959717, 0.33339500427246094, 0.33342909812927246, 0.33343505859375, 0.3334369659423828, 0.33344507217407227, 0.33344602584838867, 0.33346009254455566, 0.3334839344024658, 0.33349013328552246, 0.3335139751434326, 0.33351898193359375, 0.33352017402648926, 0.3335280418395996, 0.3335280418395996, 0.3335540294647217, 0.3335609436035156, 0.33356308937072754, 0.33356785774230957, 0.3335731029510498, 0.333575963973999, 0.33358097076416016, 0.3336069583892822, 0.3336169719696045, 0.3336188793182373, 0.3336200714111328, 0.33362698554992676, 0.333636999130249, 0.33364295959472656, 0.33364415168762207, 0.3336451053619385, 0.33365392684936523, 0.33365392684936523, 0.33365702629089355, 0.33365893363952637, 0.3336789608001709, 0.3336970806121826, 0.333698034286499, 0.3337070941925049, 0.3337218761444092, 0.3337249755859375, 0.3337268829345703, 0.33374595642089844, 0.3337538242340088, 0.333759069442749, 0.33376193046569824, 0.33376502990722656, 0.3337728977203369, 0.3337829113006592, 0.3337838649749756, 0.3337879180908203, 0.3337998390197754, 0.3338019847869873, 0.333834171295166, 0.3338499069213867, 0.3338589668273926, 0.3338608741760254, 0.33387303352355957, 0.33388805389404297, 0.33391404151916504, 0.33391594886779785, 0.3339200019836426, 0.3339250087738037, 0.33392906188964844, 0.3339509963989258, 0.3339550495147705, 0.3339729309082031, 0.33397507667541504, 0.333981990814209, 0.3339838981628418, 0.33399295806884766, 0.3340120315551758, 0.3340599536895752, 0.3340928554534912, 0.3340940475463867, 0.3341031074523926, 0.3341097831726074, 0.33411097526550293, 0.33411717414855957, 0.334118127822876, 0.3341231346130371, 0.3341238498687744, 0.33416199684143066, 0.334165096282959, 0.3341670036315918, 0.3341710567474365, 0.33417201042175293, 0.3342020511627197, 0.33420491218566895, 0.33420515060424805, 0.3342099189758301, 0.33421778678894043, 0.3342459201812744, 0.33425092697143555, 0.33426594734191895, 0.3342769145965576, 0.33427906036376953, 0.33428001403808594, 0.33428287506103516, 0.3342859745025635, 0.33431100845336914, 0.33431196212768555, 0.33431291580200195, 0.3343160152435303, 0.3343219757080078, 0.33434391021728516, 0.33434391021728516, 0.33435583114624023, 0.334414005279541, 0.334414005279541, 0.3344271183013916, 0.33443617820739746, 0.3344578742980957, 0.3344721794128418, 0.3344738483428955, 0.33449888229370117, 0.33450889587402344, 0.3345160484313965, 0.3345351219177246, 0.33455801010131836, 0.33457303047180176, 0.33458995819091797, 0.33460497856140137, 0.3346078395843506, 0.33461809158325195, 0.33461904525756836, 0.33463096618652344, 0.3346428871154785, 0.334644079208374, 0.3346540927886963, 0.334658145904541, 0.33469295501708984, 0.33469676971435547, 0.3347041606903076, 0.3347198963165283, 0.33474302291870117, 0.3347480297088623, 0.3347601890563965, 0.3347611427307129, 0.33477091789245605, 0.3347959518432617, 0.33480381965637207, 0.3348078727722168, 0.3348121643066406, 0.33483004570007324, 0.33484911918640137, 0.33486008644104004, 0.33486509323120117, 0.33487796783447266, 0.3348841667175293, 0.3348848819732666, 0.33489513397216797, 0.33490800857543945, 0.33490896224975586, 0.3349142074584961, 0.3349161148071289, 0.3349161148071289, 0.3349180221557617, 0.3349339962005615, 0.33493494987487793, 0.3349440097808838, 0.3349480628967285, 0.3349721431732178, 0.3349730968475342, 0.33498382568359375, 0.33499598503112793, 0.3350081443786621, 0.3350081443786621, 0.3350210189819336, 0.33503103256225586, 0.33504390716552734, 0.33504605293273926, 0.3350560665130615, 0.33507394790649414, 0.3350801467895508, 0.3350989818572998, 0.3351099491119385, 0.3351120948791504, 0.3351171016693115, 0.33511805534362793, 0.3351249694824219, 0.3351249694824219, 0.33515310287475586, 0.33519697189331055, 0.33521604537963867, 0.335237979888916, 0.33523988723754883, 0.3352479934692383, 0.3352510929107666, 0.3352518081665039, 0.3352799415588379, 0.3352940082550049, 0.3353078365325928, 0.33536791801452637, 0.3353750705718994, 0.3353760242462158, 0.33540797233581543, 0.33542299270629883, 0.3354320526123047, 0.3354377746582031, 0.3354511260986328, 0.33547496795654297, 0.3354759216308594, 0.3354799747467041, 0.33548593521118164, 0.3354940414428711, 0.3354949951171875, 0.33551502227783203, 0.33553409576416016, 0.3355410099029541, 0.3355588912963867, 0.3355598449707031, 0.33556699752807617, 0.33557891845703125, 0.3355870246887207, 0.33560681343078613, 0.33562588691711426, 0.3356349468231201, 0.33564305305480957, 0.3356499671936035, 0.33565497398376465, 0.33566904067993164, 0.33568906784057617, 0.33570218086242676, 0.3357090950012207, 0.33571290969848633, 0.33573412895202637, 0.33574891090393066, 0.33574891090393066, 0.3357529640197754, 0.335766077041626, 0.3357698917388916, 0.3357720375061035, 0.3358011245727539, 0.3358321189880371, 0.33583593368530273, 0.33584094047546387, 0.3358888626098633, 0.3359081745147705, 0.33594489097595215, 0.33594799041748047, 0.335968017578125, 0.3359849452972412, 0.33598899841308594, 0.3359959125518799, 0.3360600471496582, 0.33610105514526367, 0.33611011505126953, 0.33612489700317383, 0.336137056350708, 0.33615803718566895, 0.33617401123046875, 0.3361818790435791, 0.3361930847167969, 0.3362140655517578, 0.33622193336486816, 0.33622288703918457, 0.3362259864807129, 0.3362278938293457, 0.33625197410583496, 0.3362910747528076, 0.3363068103790283, 0.33634018898010254, 0.3363509178161621, 0.3363668918609619, 0.33639001846313477, 0.33639097213745117, 0.3364078998565674, 0.3364109992980957, 0.33641982078552246, 0.3364241123199463, 0.3364379405975342, 0.33645105361938477, 0.33654189109802246, 0.33658599853515625, 0.33661699295043945, 0.33662891387939453, 0.336683988571167, 0.336698055267334, 0.3367130756378174, 0.33673620223999023, 0.33673715591430664, 0.33674097061157227, 0.3367800712585449, 0.33678293228149414, 0.3368229866027832, 0.3368408679962158, 0.3368489742279053, 0.3370189666748047, 0.33709001541137695, 0.3371140956878662, 0.3372201919555664, 0.33725619316101074, 0.3372621536254883, 0.33731913566589355, 0.3373849391937256, 0.3374178409576416, 0.3374340534210205, 0.33751702308654785, 0.3375248908996582, 0.33759093284606934, 0.3377108573913574, 0.33809399604797363, 0.3381340503692627, 0.3382589817047119, 0.3383040428161621, 0.33846116065979004, 0.33855104446411133, 0.3395559787750244, 0.34038305282592773, 0.3407430648803711, 0.3414289951324463, 0.34210705757141113, 0.3424670696258545, 0.34258198738098145, 0.3426220417022705, 0.3426830768585205, 0.3427448272705078, 0.34281110763549805, 0.3428781032562256, 0.3429231643676758, 0.3429279327392578, 0.34316110610961914, 0.34319496154785156, 0.34322595596313477, 0.3432309627532959, 0.3432881832122803, 0.3433718681335449, 0.34345388412475586, 0.343472957611084, 0.34348392486572266, 0.34349894523620605, 0.3435180187225342, 0.3435389995574951, 0.34357714653015137, 0.3435969352722168, 0.3436410427093506, 0.3436439037322998, 0.3437020778656006, 0.34374117851257324, 0.34377193450927734, 0.3437919616699219, 0.34386396408081055, 0.34386777877807617, 0.3438730239868164, 0.3438739776611328, 0.3439018726348877, 0.3439171314239502, 0.3439309597015381, 0.34395909309387207, 0.343966007232666, 0.34397196769714355, 0.3440110683441162, 0.34401607513427734, 0.3440239429473877, 0.34404993057250977, 0.3440990447998047, 0.3441579341888428, 0.3441751003265381, 0.3441798686981201, 0.3441908359527588, 0.34421396255493164, 0.34421801567077637, 0.3442268371582031, 0.3442521095275879, 0.3442530632019043, 0.3442678451538086, 0.3442709445953369, 0.3442821502685547, 0.34430813789367676, 0.344329833984375, 0.3443310260772705, 0.3443479537963867, 0.34435296058654785, 0.34435391426086426, 0.3443601131439209, 0.34439897537231445, 0.34441399574279785, 0.344419002532959, 0.34444689750671387, 0.34445810317993164, 0.34447503089904785, 0.34452009201049805, 0.3445301055908203, 0.34453701972961426, 0.34456396102905273, 0.34458494186401367, 0.34460997581481934, 0.34461402893066406, 0.3446168899536133, 0.3446221351623535, 0.34462690353393555, 0.34470295906066895, 0.34473299980163574, 0.34474897384643555, 0.34477806091308594, 0.34483885765075684, 0.3448448181152344, 0.3448817729949951, 0.34489989280700684, 0.34491515159606934, 0.3449230194091797, 0.34493494033813477, 0.3449380397796631, 0.3449430465698242, 0.34496092796325684, 0.3449881076812744, 0.34504079818725586, 0.3450489044189453, 0.34505414962768555, 0.34507012367248535, 0.3450789451599121, 0.34508180618286133, 0.3450939655303955, 0.34510207176208496, 0.345106840133667, 0.34511780738830566, 0.3451411724090576, 0.3451838493347168, 0.34519195556640625, 0.3451969623565674, 0.3451981544494629, 0.3452119827270508, 0.3452448844909668, 0.3452589511871338, 0.34528589248657227, 0.3452889919281006, 0.34532594680786133, 0.3453350067138672, 0.3453559875488281, 0.34537506103515625, 0.3453960418701172, 0.3454129695892334, 0.345426082611084, 0.3454718589782715, 0.3454890251159668, 0.34549784660339355, 0.3455030918121338, 0.34552717208862305, 0.3455350399017334, 0.34556078910827637, 0.3455629348754883, 0.3456149101257324, 0.3456540107727051, 0.3456690311431885, 0.34568214416503906, 0.345721960067749, 0.34572792053222656, 0.3457319736480713, 0.3457460403442383, 0.3458089828491211, 0.34581494331359863, 0.3458240032196045, 0.3458271026611328, 0.34584808349609375, 0.3458709716796875, 0.3458750247955322, 0.34589195251464844, 0.34590792655944824, 0.34596920013427734, 0.34596991539001465, 0.3459899425506592, 0.3460390567779541, 0.3460829257965088, 0.3460869789123535, 0.3460988998413086, 0.34613895416259766, 0.34615492820739746, 0.3461570739746094, 0.3461599349975586, 0.34616899490356445, 0.3461730480194092, 0.346189022064209, 0.34627485275268555, 0.34632086753845215, 0.3463258743286133, 0.3463261127471924, 0.3463561534881592, 0.34639596939086914, 0.3464019298553467, 0.3464028835296631, 0.3464069366455078, 0.346419095993042, 0.3464229106903076, 0.3464350700378418, 0.3464529514312744, 0.3464980125427246, 0.34650588035583496, 0.346513032913208, 0.34655284881591797, 0.3465590476989746, 0.3465750217437744, 0.3466010093688965, 0.34661102294921875, 0.34662389755249023, 0.3466660976409912, 0.34673404693603516, 0.34674906730651855, 0.34676504135131836, 0.3468189239501953, 0.34682393074035645, 0.3468310832977295, 0.3468799591064453, 0.34689807891845703, 0.3470330238342285, 0.34704089164733887, 0.34705400466918945, 0.3471221923828125, 0.34717607498168945, 0.34723496437072754, 0.3472459316253662, 0.34725308418273926, 0.3473351001739502, 0.3473539352416992, 0.3473958969116211, 0.34740591049194336, 0.3474249839782715, 0.3474998474121094, 0.3475160598754883, 0.34752702713012695, 0.347545862197876, 0.3476879596710205, 0.3478209972381592, 0.34784507751464844, 0.3479299545288086, 0.3479630947113037, 0.34809207916259766, 0.3481440544128418, 0.34842610359191895, 0.348552942276001, 0.34860897064208984, 0.3486769199371338, 0.34880495071411133, 0.34885311126708984, 0.34908008575439453, 0.34961915016174316, 0.3496279716491699, 0.3497648239135742, 0.3522820472717285, 0.35250306129455566, 0.35359621047973633, 0.35461997985839844, 0.3548710346221924, 0.3554971218109131, 0.3555278778076172, 0.35568714141845703, 0.3557729721069336, 0.3557858467102051, 0.3558628559112549, 0.35606813430786133, 0.3562757968902588, 0.35655999183654785, 0.3568718433380127, 0.35699892044067383, 0.35716915130615234, 0.3572719097137451, 0.35730791091918945, 0.3574869632720947, 0.3578050136566162, 0.3578300476074219, 0.3579220771789551, 0.3586599826812744, 0.35965800285339355, 0.40105390548706055, 0.40197277069091797, 0.40239500999450684, 0.4030120372772217, 0.4030418395996094, 0.4036591053009033, 0.4046471118927002, 0.40465688705444336, 0.4049501419067383, 0.4071168899536133, 0.40720295906066895, 0.4088010787963867, 0.4089200496673584, 0.40961599349975586, 0.4109001159667969, 0.4112389087677002, 0.4118351936340332, 0.4124610424041748, 0.4128549098968506, 0.4131171703338623, 0.413128137588501, 0.4134500026702881, 0.4135620594024658, 0.41371583938598633, 0.414078950881958, 0.4148890972137451, 0.4149439334869385, 0.4154930114746094, 0.4156680107116699, 0.4158189296722412, 0.4161360263824463, 0.41681599617004395, 0.41699790954589844, 0.4181699752807617, 0.41823792457580566, 0.4196949005126953, 0.4197521209716797, 0.42011189460754395, 0.4212779998779297, 0.4225940704345703, 0.42285704612731934, 0.42433786392211914, 0.42453479766845703, 0.42491793632507324, 0.4256711006164551, 0.4283640384674072, 0.4292759895324707]</t>
+  </si>
+  <si>
+    <t>[0.2924971580505371, 0.29269886016845703, 0.2928149700164795, 0.2931227684020996, 0.29317402839660645, 0.2936110496520996, 0.29410600662231445, 0.29413795471191406, 0.29427313804626465, 0.2944910526275635, 0.29462504386901855, 0.2948319911956787, 0.2948470115661621, 0.2972249984741211, 0.2972879409790039, 0.29788684844970703, 0.2995939254760742, 0.30032896995544434, 0.3003859519958496, 0.3004441261291504, 0.300584077835083, 0.3008768558502197, 0.30090999603271484, 0.3014400005340576, 0.30152177810668945, 0.30158400535583496, 0.3017261028289795, 0.30174708366394043, 0.30178284645080566, 0.3018059730529785, 0.30186986923217773, 0.3019890785217285, 0.3020288944244385, 0.3025522232055664, 0.3025641441345215, 0.3025779724121094, 0.30259084701538086, 0.3026609420776367, 0.30273914337158203, 0.3027479648590088, 0.3027799129486084, 0.303070068359375, 0.3031809329986572, 0.30320191383361816, 0.3032379150390625, 0.3033480644226074, 0.30336689949035645, 0.3033769130706787, 0.30339598655700684, 0.3034088611602783, 0.3034090995788574, 0.30341291427612305, 0.30343198776245117, 0.3035590648651123, 0.30359411239624023, 0.3037228584289551, 0.3037679195404053, 0.3038201332092285, 0.30382704734802246, 0.3038640022277832, 0.30390000343322754, 0.30392003059387207, 0.3039438724517822, 0.3040778636932373, 0.3040809631347656, 0.30410099029541016, 0.30411195755004883, 0.3041231632232666, 0.3041369915008545, 0.30414700508117676, 0.30426979064941406, 0.30437183380126953, 0.30439209938049316, 0.304394006729126, 0.30456113815307617, 0.3045670986175537, 0.30458998680114746, 0.30463099479675293, 0.3047618865966797, 0.3049018383026123, 0.3049590587615967, 0.3050100803375244, 0.30518198013305664, 0.3054640293121338, 0.3055911064147949, 0.30577707290649414, 0.3058130741119385, 0.3058309555053711, 0.3058900833129883, 0.3059108257293701, 0.30599498748779297, 0.306102991104126, 0.30629515647888184, 0.30634188652038574, 0.3067901134490967, 0.3070399761199951, 0.30716705322265625, 0.3075220584869385, 0.3077208995819092, 0.3082602024078369, 0.31012988090515137, 0.31051015853881836, 0.3107028007507324, 0.3110239505767822, 0.3110370635986328, 0.3111541271209717, 0.3112471103668213, 0.31137895584106445, 0.31142401695251465, 0.3115079402923584, 0.31156015396118164, 0.3116450309753418, 0.3117339611053467, 0.311769962310791, 0.31184887886047363, 0.31185412406921387, 0.3118710517883301, 0.31197404861450195, 0.31220507621765137, 0.3123040199279785, 0.3123159408569336, 0.3123290538787842, 0.31241893768310547, 0.3124568462371826, 0.31249499320983887, 0.3125622272491455, 0.31259703636169434, 0.3126339912414551, 0.3126668930053711, 0.3126819133758545, 0.3127920627593994, 0.31283116340637207, 0.3128499984741211, 0.31293702125549316, 0.3129410743713379, 0.31299400329589844, 0.31320714950561523, 0.31327009201049805, 0.31337904930114746, 0.3134009838104248, 0.313446044921875, 0.31348204612731934, 0.3135080337524414, 0.31353211402893066, 0.3135700225830078, 0.31362080574035645, 0.3136758804321289, 0.3137340545654297, 0.31376218795776367, 0.313770055770874, 0.31377220153808594, 0.3138442039489746, 0.3139331340789795, 0.31395506858825684, 0.3139829635620117, 0.3139841556549072, 0.3139939308166504, 0.31404709815979004, 0.31404781341552734, 0.3140830993652344, 0.3141040802001953, 0.31423115730285645, 0.3142669200897217, 0.3142688274383545, 0.31429100036621094, 0.31429195404052734, 0.3143351078033447, 0.31434202194213867, 0.3143610954284668, 0.31442713737487793, 0.314467191696167, 0.3144841194152832, 0.3145010471343994, 0.31450605392456055, 0.31450891494750977, 0.314586877822876, 0.314586877822876, 0.31459593772888184, 0.3146038055419922, 0.31462812423706055, 0.31463098526000977, 0.3146390914916992, 0.31464600563049316, 0.3146510124206543, 0.3146638870239258, 0.31467700004577637, 0.31470608711242676, 0.31470704078674316, 0.314716100692749, 0.31473302841186523, 0.3147392272949219, 0.3147749900817871, 0.31479620933532715, 0.31481003761291504, 0.31481194496154785, 0.3148219585418701, 0.3148629665374756, 0.31487607955932617, 0.31490087509155273, 0.3149130344390869, 0.31493592262268066, 0.3149590492248535, 0.31498193740844727, 0.31499791145324707, 0.31502389907836914, 0.3150920867919922, 0.3151068687438965, 0.31519484519958496, 0.315234899520874, 0.3152430057525635, 0.31525278091430664, 0.3152649402618408, 0.3152740001678467, 0.3152740001678467, 0.3152799606323242, 0.31531500816345215, 0.3153259754180908, 0.3153350353240967, 0.315338134765625, 0.3153409957885742, 0.31536102294921875, 0.3153860569000244, 0.31540393829345703, 0.3154289722442627, 0.31543803215026855, 0.3154618740081787, 0.3154640197753906, 0.31548094749450684, 0.31548500061035156, 0.31551599502563477, 0.3155500888824463, 0.31555795669555664, 0.31556200981140137, 0.3155651092529297, 0.31557703018188477, 0.31560277938842773, 0.315654993057251, 0.31566405296325684, 0.3156900405883789, 0.31571292877197266, 0.31574416160583496, 0.31580209732055664, 0.3158390522003174, 0.3158588409423828, 0.31587791442871094, 0.31589198112487793, 0.31590914726257324, 0.3159141540527344, 0.3159301280975342, 0.3159499168395996, 0.31595587730407715, 0.31601595878601074, 0.31603097915649414, 0.31606197357177734, 0.3160829544067383, 0.31611108779907227, 0.31615400314331055, 0.3161630630493164, 0.3161931037902832, 0.31621599197387695, 0.31624698638916016, 0.31626415252685547, 0.31629300117492676, 0.31629300117492676, 0.3162989616394043, 0.31630802154541016, 0.31641387939453125, 0.3164401054382324, 0.31644487380981445, 0.31644701957702637, 0.31647300720214844, 0.3164951801300049, 0.31651806831359863, 0.31652307510375977, 0.31655001640319824, 0.31662583351135254, 0.31664395332336426, 0.316662073135376, 0.31667089462280273, 0.31670308113098145, 0.31671786308288574, 0.31684398651123047, 0.3168468475341797, 0.316892147064209, 0.3169281482696533, 0.316972017288208, 0.31697797775268555, 0.3169870376586914, 0.31702184677124023, 0.3170909881591797, 0.3170969486236572, 0.3173248767852783, 0.31734299659729004, 0.31740903854370117, 0.31751084327697754, 0.31757307052612305, 0.3175809383392334, 0.3177027702331543, 0.31771397590637207, 0.31777501106262207, 0.3178858757019043, 0.3179359436035156, 0.31795597076416016, 0.3179609775543213, 0.3180088996887207, 0.31806302070617676, 0.3181729316711426, 0.3182668685913086, 0.3184950351715088, 0.3185160160064697, 0.318540096282959, 0.3185570240020752, 0.31864190101623535, 0.31881093978881836, 0.3188350200653076, 0.31891584396362305, 0.31929898262023926, 0.3196909427642822, 0.319720983505249, 0.31972193717956543, 0.32015085220336914, 0.3207080364227295, 0.32089996337890625, 0.32097315788269043, 0.3214991092681885, 0.3215939998626709, 0.32163310050964355, 0.32163500785827637, 0.3216588497161865, 0.3216700553894043, 0.32169222831726074, 0.3218832015991211, 0.321897029876709, 0.3219289779663086, 0.3220839500427246, 0.3221578598022461, 0.3221728801727295, 0.3221781253814697, 0.32219982147216797, 0.3227410316467285, 0.32274413108825684, 0.3227570056915283, 0.3227808475494385, 0.3228120803833008, 0.322829008102417, 0.3229191303253174, 0.3229529857635498, 0.3229560852050781, 0.3232450485229492, 0.32328009605407715, 0.3232848644256592, 0.3232882022857666, 0.32334208488464355, 0.32335805892944336, 0.3234269618988037, 0.32343292236328125, 0.3235628604888916, 0.32356905937194824, 0.32361888885498047, 0.32363200187683105, 0.32365894317626953, 0.3236820697784424, 0.32369089126586914, 0.32379794120788574, 0.32384204864501953, 0.32384514808654785, 0.32384610176086426, 0.323897123336792, 0.323915958404541, 0.32398486137390137, 0.3240058422088623, 0.3240070343017578, 0.3240211009979248, 0.32402920722961426, 0.3240690231323242, 0.32408905029296875, 0.32425999641418457, 0.3242640495300293, 0.32428693771362305, 0.32429981231689453, 0.32433605194091797, 0.32436585426330566, 0.3244209289550781, 0.3244318962097168, 0.32444000244140625, 0.3245091438293457, 0.3245270252227783, 0.3245518207550049, 0.3245730400085449, 0.32458996772766113, 0.32460904121398926, 0.3246290683746338, 0.3246488571166992, 0.32471203804016113, 0.3247358798980713, 0.3247678279876709, 0.3247969150543213, 0.3247990608215332, 0.32480788230895996, 0.3248131275177002, 0.32482314109802246, 0.3248631954193115, 0.32486701011657715, 0.32489895820617676, 0.32490992546081543, 0.32494211196899414, 0.32506895065307617, 0.3250718116760254, 0.325084924697876, 0.3251969814300537, 0.32523679733276367, 0.325300931930542, 0.3253028392791748, 0.3253300189971924, 0.32535481452941895, 0.3253788948059082, 0.32548999786376953, 0.32550787925720215, 0.3255140781402588, 0.3255269527435303, 0.325592041015625, 0.32561802864074707, 0.325624942779541, 0.32564520835876465, 0.3256521224975586, 0.32566308975219727, 0.3256990909576416, 0.32570910453796387, 0.3257150650024414, 0.32571887969970703, 0.32572007179260254, 0.32576584815979004, 0.32576608657836914, 0.32579898834228516, 0.32579994201660156, 0.32587599754333496, 0.3258941173553467, 0.32590579986572266, 0.32591986656188965, 0.32591986656188965, 0.32594895362854004, 0.3259599208831787, 0.3260619640350342, 0.3261141777038574, 0.32611513137817383, 0.32611513137817383, 0.326124906539917, 0.3261270523071289, 0.3261280059814453, 0.32613205909729004, 0.32613301277160645, 0.3261699676513672, 0.3261699676513672, 0.32617878913879395, 0.3261849880218506, 0.32619595527648926, 0.3262009620666504, 0.32621192932128906, 0.326246976852417, 0.3262641429901123, 0.3263070583343506, 0.3263120651245117, 0.3263399600982666, 0.32634687423706055, 0.32637691497802734, 0.3263850212097168, 0.326387882232666, 0.32640600204467773, 0.32642698287963867, 0.32645487785339355, 0.3264789581298828, 0.32648181915283203, 0.32648205757141113, 0.32649707794189453, 0.32649707794189453, 0.3265068531036377, 0.3265070915222168, 0.3265390396118164, 0.32654881477355957, 0.3265519142150879, 0.32656002044677734, 0.32656192779541016, 0.3265800476074219, 0.3266279697418213, 0.3266298770904541, 0.3266310691833496, 0.32663488388061523, 0.32666516304016113, 0.32666802406311035, 0.32667088508605957, 0.3266751766204834, 0.3266761302947998, 0.3266880512237549, 0.326693058013916, 0.3267090320587158, 0.3267221450805664, 0.3267378807067871, 0.32674193382263184, 0.3267638683319092, 0.32683396339416504, 0.32683706283569336, 0.32686495780944824, 0.32686591148376465, 0.32686710357666016, 0.32686805725097656, 0.32688283920288086, 0.3268909454345703, 0.326901912689209, 0.32691192626953125, 0.32694101333618164, 0.32694411277770996, 0.3269469738006592, 0.32697296142578125, 0.3269820213317871, 0.3269829750061035, 0.32698822021484375, 0.3269939422607422, 0.3270139694213867, 0.3270411491394043, 0.32704687118530273, 0.3270840644836426, 0.3270900249481201, 0.3270909786224365, 0.32711100578308105, 0.32711291313171387, 0.3271150588989258, 0.3271200656890869, 0.32712793350219727, 0.3271369934082031, 0.32714200019836426, 0.3271481990814209, 0.32715797424316406, 0.327160120010376, 0.3271620273590088, 0.32718801498413086, 0.3271908760070801, 0.3271939754486084, 0.3271958827972412, 0.32720494270324707, 0.3272130489349365, 0.3272252082824707, 0.3272359371185303, 0.3272678852081299, 0.32727909088134766, 0.32731199264526367, 0.3273138999938965, 0.3273451328277588, 0.32738590240478516, 0.3274071216583252, 0.32743310928344727, 0.327441930770874, 0.32749080657958984, 0.327498197555542, 0.32752084732055664, 0.3275611400604248, 0.327564001083374, 0.32756495475769043, 0.32756781578063965, 0.32761406898498535, 0.3276340961456299, 0.32766103744506836, 0.327678918838501, 0.32772397994995117, 0.3277308940887451, 0.32773590087890625, 0.32773804664611816, 0.327739953994751, 0.327739953994751, 0.32778310775756836, 0.32784008979797363, 0.3278679847717285, 0.3278839588165283, 0.32791686058044434, 0.3279449939727783, 0.3279600143432617, 0.32801294326782227, 0.3280367851257324, 0.32805705070495605, 0.3280670642852783, 0.32808399200439453, 0.32809996604919434, 0.32810497283935547, 0.32811784744262695, 0.3282010555267334, 0.328204870223999, 0.3282449245452881, 0.32828593254089355, 0.3283088207244873, 0.3283088207244873, 0.3283839225769043, 0.32842087745666504, 0.32843995094299316, 0.3284580707550049, 0.3284759521484375, 0.32848691940307617, 0.3285079002380371, 0.328549861907959, 0.32857513427734375, 0.3285951614379883, 0.32860493659973145, 0.328765869140625, 0.3287661075592041, 0.32896995544433594, 0.3289909362792969, 0.3289909362792969, 0.32923197746276855, 0.32932400703430176, 0.32941579818725586, 0.3296999931335449, 0.3298959732055664, 0.3299520015716553, 0.3299551010131836, 0.33018016815185547, 0.3302309513092041, 0.3302888870239258, 0.3302891254425049, 0.3303208351135254, 0.3306241035461426, 0.3308141231536865, 0.33089613914489746, 0.3309190273284912, 0.3309669494628906, 0.33104705810546875, 0.33104705810546875, 0.33125996589660645, 0.3315401077270508, 0.3315620422363281, 0.3319430351257324, 0.3327481746673584, 0.33295512199401855, 0.3329639434814453, 0.33297300338745117, 0.33328914642333984, 0.3332991600036621, 0.33338093757629395, 0.33345603942871094, 0.33362698554992676, 0.3336520195007324, 0.3336820602416992, 0.33368921279907227, 0.3337819576263428, 0.33382296562194824, 0.33385586738586426, 0.3339078426361084, 0.3339219093322754, 0.3339269161224365, 0.33410096168518066, 0.33414196968078613, 0.3341500759124756, 0.3342630863189697, 0.33426499366760254, 0.3343219757080078, 0.3343789577484131, 0.33438897132873535, 0.3344240188598633, 0.33446288108825684, 0.33449316024780273, 0.334514856338501, 0.3345301151275635, 0.33483004570007324, 0.3348550796508789, 0.3349580764770508, 0.3349590301513672, 0.3349771499633789, 0.3349900245666504, 0.33509182929992676, 0.3350992202758789, 0.3351559638977051, 0.3351728916168213, 0.3352329730987549, 0.3352479934692383, 0.3352699279785156, 0.33527708053588867, 0.33533406257629395, 0.33538007736206055, 0.3354160785675049, 0.33542704582214355, 0.33544492721557617, 0.33550310134887695, 0.3355381488800049, 0.3355560302734375, 0.3355581760406494, 0.33556199073791504, 0.33571410179138184, 0.3358440399169922, 0.3358650207519531, 0.33600497245788574, 0.33603882789611816, 0.33606505393981934, 0.3361239433288574, 0.3361330032348633, 0.3361489772796631, 0.33615994453430176, 0.33623719215393066, 0.3362388610839844, 0.3363161087036133, 0.33632493019104004, 0.33635401725769043, 0.33639001846313477, 0.33640289306640625, 0.3364369869232178, 0.3364429473876953, 0.33647894859313965, 0.33647918701171875, 0.33657407760620117, 0.3365769386291504, 0.33658814430236816, 0.3366410732269287, 0.33664798736572266, 0.336698055267334, 0.33670997619628906, 0.33671092987060547, 0.336716890335083, 0.33673596382141113, 0.3367769718170166, 0.3367900848388672, 0.33681583404541016, 0.336895227432251, 0.3368990421295166, 0.33692097663879395, 0.33696699142456055, 0.3369741439819336, 0.3369920253753662, 0.33699703216552734, 0.3370239734649658, 0.3371000289916992, 0.33710217475891113, 0.3371400833129883, 0.33714818954467773, 0.3371720314025879, 0.33728718757629395, 0.3372981548309326, 0.3373119831085205, 0.33732104301452637, 0.3373219966888428, 0.3373289108276367, 0.3373429775238037, 0.33736205101013184, 0.33738112449645996, 0.33739399909973145, 0.33740997314453125, 0.3374669551849365, 0.33747100830078125, 0.33748412132263184, 0.3375120162963867, 0.3375260829925537, 0.33752894401550293, 0.3375411033630371, 0.3375570774078369, 0.33759021759033203, 0.33759284019470215, 0.3376038074493408, 0.33760499954223633, 0.33760905265808105, 0.3376479148864746, 0.33765292167663574, 0.3377361297607422, 0.33775997161865234, 0.33783507347106934, 0.337846040725708, 0.3378589153289795, 0.337860107421875, 0.3378639221191406, 0.33786797523498535, 0.3379650115966797, 0.33797502517700195, 0.3380141258239746, 0.338062047958374, 0.3380711078643799, 0.3380751609802246, 0.33809518814086914, 0.3381040096282959, 0.3381311893463135, 0.3381838798522949, 0.33818602561950684, 0.3381941318511963, 0.3381989002227783, 0.33821892738342285, 0.338270902633667, 0.3382711410522461, 0.33832693099975586, 0.3383660316467285, 0.33837008476257324, 0.33840203285217285, 0.33843517303466797, 0.3384850025177002, 0.3385169506072998, 0.33854007720947266, 0.3385660648345947, 0.3386411666870117, 0.33869099617004395, 0.3387739658355713, 0.3387870788574219, 0.3387908935546875, 0.33879899978637695, 0.33883190155029297, 0.3388841152191162, 0.3389320373535156, 0.33896303176879883, 0.3389720916748047, 0.3390378952026367, 0.3391110897064209, 0.33916306495666504, 0.3391690254211426, 0.3391730785369873, 0.33922910690307617, 0.33929896354675293, 0.339385986328125, 0.3394138813018799, 0.3394150733947754, 0.33948493003845215, 0.3395390510559082, 0.3396270275115967, 0.33972811698913574, 0.3397510051727295, 0.3397860527038574, 0.33994412422180176, 0.3400590419769287, 0.3400759696960449, 0.34009385108947754, 0.340116024017334, 0.34030699729919434, 0.340425968170166, 0.34047698974609375, 0.3405148983001709, 0.3405640125274658, 0.34058594703674316, 0.34061384201049805, 0.34090089797973633, 0.3411529064178467, 0.34163808822631836, 0.3418710231781006, 0.34204816818237305, 0.3421509265899658, 0.34280991554260254, 0.3430609703063965, 0.3435831069946289, 0.3436429500579834, 0.3437540531158447, 0.34407496452331543, 0.3443160057067871, 0.34470081329345703, 0.34476590156555176, 0.3449990749359131, 0.34542202949523926, 0.34574198722839355, 0.3457651138305664, 0.34589695930480957, 0.3459198474884033, 0.3460209369659424, 0.3462100028991699, 0.34651803970336914, 0.3465311527252197, 0.34656405448913574, 0.34664106369018555, 0.3469679355621338, 0.3470730781555176, 0.3471639156341553, 0.3473210334777832, 0.347398042678833, 0.3474428653717041, 0.3475630283355713, 0.34758806228637695, 0.3476870059967041, 0.3477318286895752, 0.3478219509124756, 0.34782981872558594, 0.34791111946105957, 0.34801793098449707, 0.3480348587036133, 0.3482041358947754, 0.3483269214630127, 0.34833502769470215, 0.348344087600708, 0.34835290908813477, 0.34838390350341797, 0.34841418266296387, 0.3484680652618408, 0.34851598739624023, 0.3485219478607178, 0.3485431671142578, 0.348560094833374, 0.34863901138305664, 0.34866976737976074, 0.3489081859588623, 0.3489561080932617, 0.3489680290222168, 0.34899020195007324, 0.34900593757629395, 0.3491208553314209, 0.3491530418395996, 0.3492147922515869, 0.34925198554992676, 0.34955906867980957, 0.3495779037475586, 0.34960412979125977, 0.34975409507751465, 0.349808931350708, 0.34981703758239746, 0.34983301162719727, 0.3498828411102295, 0.34999513626098633, 0.3502500057220459, 0.3503739833831787, 0.3504049777984619, 0.35042405128479004, 0.3505518436431885, 0.3505570888519287, 0.35065388679504395, 0.3507049083709717, 0.35071396827697754, 0.350801944732666, 0.35097217559814453, 0.3512887954711914, 0.35185885429382324, 0.3522670269012451, 0.3528320789337158, 0.3531510829925537, 0.3534369468688965, 0.3537561893463135, 0.35476088523864746, 0.3553588390350342, 0.3568761348724365, 0.357280969619751, 0.3578450679779053, 0.35851502418518066, 0.35879993438720703, 0.35916805267333984, 0.3593158721923828, 0.3593630790710449, 0.3594021797180176, 0.35964107513427734, 0.3601949214935303, 0.3602931499481201, 0.3603219985961914, 0.3607199192047119, 0.3607761859893799, 0.36084508895874023, 0.3616299629211426, 0.3616759777069092, 0.36170196533203125, 0.3622000217437744, 0.3623330593109131, 0.36278605461120605, 0.363433837890625, 0.3635518550872803, 0.36545515060424805, 0.369844913482666, 0.37140893936157227, 0.37166810035705566, 0.37167811393737793, 0.37256312370300293, 0.37467193603515625, 0.3907458782196045, 0.3974769115447998, 0.40386295318603516, 0.4041409492492676, 0.40474486351013184, 0.4111659526824951, 0.4119241237640381, 0.4120039939880371, 0.4123358726501465, 0.412891149520874, 0.41299986839294434, 0.41338396072387695, 0.41616010665893555, 0.4199869632720947, 0.42330384254455566, 0.4235420227050781, 0.4238569736480713, 0.4253580570220947, 0.4256420135498047, 0.4268040657043457, 0.42683887481689453, 0.4277510643005371, 0.4277660846710205, 0.4325859546661377, 0.4327421188354492, 0.4327518939971924, 0.4330098628997803]</t>
   </si>
 </sst>
 </file>
